--- a/output/version3/test/20-15/MARL/IL/RL-RL with pt/(RL+RL) test results.xlsx
+++ b/output/version3/test/20-15/MARL/IL/RL-RL with pt/(RL+RL) test results.xlsx
@@ -471,37 +471,37 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>858</v>
+        <v>826</v>
       </c>
       <c r="C2" t="n">
-        <v>856</v>
+        <v>854</v>
       </c>
       <c r="D2" t="n">
-        <v>973</v>
+        <v>1060</v>
       </c>
       <c r="E2" t="n">
-        <v>963</v>
+        <v>879</v>
       </c>
       <c r="F2" t="n">
-        <v>949</v>
+        <v>902</v>
       </c>
       <c r="G2" t="n">
-        <v>830</v>
+        <v>759</v>
       </c>
       <c r="H2" t="n">
-        <v>853</v>
+        <v>785</v>
       </c>
       <c r="I2" t="n">
-        <v>985</v>
+        <v>1034</v>
       </c>
       <c r="J2" t="n">
-        <v>922</v>
+        <v>897</v>
       </c>
       <c r="K2" t="n">
-        <v>932</v>
+        <v>958</v>
       </c>
       <c r="L2" t="n">
-        <v>912.1</v>
+        <v>895.4</v>
       </c>
     </row>
     <row r="3">
@@ -509,37 +509,37 @@
         <v>10</v>
       </c>
       <c r="B3" t="n">
-        <v>881</v>
+        <v>959</v>
       </c>
       <c r="C3" t="n">
-        <v>1196</v>
+        <v>894</v>
       </c>
       <c r="D3" t="n">
-        <v>1072</v>
+        <v>1036</v>
       </c>
       <c r="E3" t="n">
-        <v>1076</v>
+        <v>961</v>
       </c>
       <c r="F3" t="n">
-        <v>792</v>
+        <v>804</v>
       </c>
       <c r="G3" t="n">
-        <v>1052</v>
+        <v>1013</v>
       </c>
       <c r="H3" t="n">
-        <v>800</v>
+        <v>851</v>
       </c>
       <c r="I3" t="n">
-        <v>988</v>
+        <v>949</v>
       </c>
       <c r="J3" t="n">
-        <v>971</v>
+        <v>936</v>
       </c>
       <c r="K3" t="n">
-        <v>1012</v>
+        <v>1025</v>
       </c>
       <c r="L3" t="n">
-        <v>984</v>
+        <v>942.8</v>
       </c>
     </row>
     <row r="4">
@@ -547,37 +547,37 @@
         <v>11</v>
       </c>
       <c r="B4" t="n">
-        <v>765</v>
+        <v>1028</v>
       </c>
       <c r="C4" t="n">
-        <v>808</v>
+        <v>825</v>
       </c>
       <c r="D4" t="n">
-        <v>776</v>
+        <v>1059</v>
       </c>
       <c r="E4" t="n">
-        <v>730</v>
+        <v>836</v>
       </c>
       <c r="F4" t="n">
-        <v>865</v>
+        <v>907</v>
       </c>
       <c r="G4" t="n">
-        <v>771</v>
+        <v>945</v>
       </c>
       <c r="H4" t="n">
         <v>872</v>
       </c>
       <c r="I4" t="n">
-        <v>871</v>
+        <v>770</v>
       </c>
       <c r="J4" t="n">
-        <v>799</v>
+        <v>1010</v>
       </c>
       <c r="K4" t="n">
-        <v>840</v>
+        <v>777</v>
       </c>
       <c r="L4" t="n">
-        <v>809.7</v>
+        <v>902.9</v>
       </c>
     </row>
     <row r="5">
@@ -585,37 +585,37 @@
         <v>12</v>
       </c>
       <c r="B5" t="n">
-        <v>883</v>
+        <v>998</v>
       </c>
       <c r="C5" t="n">
-        <v>945</v>
+        <v>839</v>
       </c>
       <c r="D5" t="n">
-        <v>776</v>
+        <v>845</v>
       </c>
       <c r="E5" t="n">
-        <v>782</v>
+        <v>785</v>
       </c>
       <c r="F5" t="n">
-        <v>801</v>
+        <v>965</v>
       </c>
       <c r="G5" t="n">
-        <v>968</v>
+        <v>908</v>
       </c>
       <c r="H5" t="n">
-        <v>776</v>
+        <v>983</v>
       </c>
       <c r="I5" t="n">
-        <v>956</v>
+        <v>909</v>
       </c>
       <c r="J5" t="n">
-        <v>788</v>
+        <v>807</v>
       </c>
       <c r="K5" t="n">
-        <v>825</v>
+        <v>838</v>
       </c>
       <c r="L5" t="n">
-        <v>850</v>
+        <v>887.7</v>
       </c>
     </row>
     <row r="6">
@@ -623,37 +623,37 @@
         <v>13</v>
       </c>
       <c r="B6" t="n">
-        <v>667</v>
+        <v>716</v>
       </c>
       <c r="C6" t="n">
-        <v>753</v>
+        <v>678</v>
       </c>
       <c r="D6" t="n">
-        <v>684</v>
+        <v>755</v>
       </c>
       <c r="E6" t="n">
-        <v>806</v>
+        <v>713</v>
       </c>
       <c r="F6" t="n">
-        <v>646</v>
+        <v>763</v>
       </c>
       <c r="G6" t="n">
-        <v>879</v>
+        <v>798</v>
       </c>
       <c r="H6" t="n">
-        <v>663</v>
+        <v>647</v>
       </c>
       <c r="I6" t="n">
-        <v>731</v>
+        <v>894</v>
       </c>
       <c r="J6" t="n">
-        <v>664</v>
+        <v>881</v>
       </c>
       <c r="K6" t="n">
-        <v>663</v>
+        <v>845</v>
       </c>
       <c r="L6" t="n">
-        <v>715.6</v>
+        <v>769</v>
       </c>
     </row>
     <row r="7">
@@ -661,37 +661,37 @@
         <v>14</v>
       </c>
       <c r="B7" t="n">
-        <v>873</v>
+        <v>747</v>
       </c>
       <c r="C7" t="n">
-        <v>954</v>
+        <v>883</v>
       </c>
       <c r="D7" t="n">
-        <v>786</v>
+        <v>821</v>
       </c>
       <c r="E7" t="n">
-        <v>955</v>
+        <v>826</v>
       </c>
       <c r="F7" t="n">
-        <v>893</v>
+        <v>903</v>
       </c>
       <c r="G7" t="n">
-        <v>808</v>
+        <v>1084</v>
       </c>
       <c r="H7" t="n">
-        <v>807</v>
+        <v>812</v>
       </c>
       <c r="I7" t="n">
-        <v>868</v>
+        <v>800</v>
       </c>
       <c r="J7" t="n">
-        <v>816</v>
+        <v>867</v>
       </c>
       <c r="K7" t="n">
-        <v>842</v>
+        <v>860</v>
       </c>
       <c r="L7" t="n">
-        <v>860.2</v>
+        <v>860.3</v>
       </c>
     </row>
     <row r="8">
@@ -699,37 +699,37 @@
         <v>15</v>
       </c>
       <c r="B8" t="n">
-        <v>737</v>
+        <v>1013</v>
       </c>
       <c r="C8" t="n">
-        <v>844</v>
+        <v>826</v>
       </c>
       <c r="D8" t="n">
-        <v>779</v>
+        <v>823</v>
       </c>
       <c r="E8" t="n">
-        <v>930</v>
+        <v>730</v>
       </c>
       <c r="F8" t="n">
-        <v>821</v>
+        <v>808</v>
       </c>
       <c r="G8" t="n">
-        <v>831</v>
+        <v>836</v>
       </c>
       <c r="H8" t="n">
-        <v>927</v>
+        <v>848</v>
       </c>
       <c r="I8" t="n">
-        <v>889</v>
+        <v>860</v>
       </c>
       <c r="J8" t="n">
-        <v>884</v>
+        <v>846</v>
       </c>
       <c r="K8" t="n">
-        <v>859</v>
+        <v>1031</v>
       </c>
       <c r="L8" t="n">
-        <v>850.1</v>
+        <v>862.1</v>
       </c>
     </row>
     <row r="9">
@@ -737,37 +737,37 @@
         <v>16</v>
       </c>
       <c r="B9" t="n">
-        <v>933</v>
+        <v>932</v>
       </c>
       <c r="C9" t="n">
-        <v>1121</v>
+        <v>841</v>
       </c>
       <c r="D9" t="n">
-        <v>860</v>
+        <v>904</v>
       </c>
       <c r="E9" t="n">
-        <v>848</v>
+        <v>793</v>
       </c>
       <c r="F9" t="n">
-        <v>878</v>
+        <v>871</v>
       </c>
       <c r="G9" t="n">
-        <v>1006</v>
+        <v>767</v>
       </c>
       <c r="H9" t="n">
-        <v>971</v>
+        <v>939</v>
       </c>
       <c r="I9" t="n">
-        <v>823</v>
+        <v>815</v>
       </c>
       <c r="J9" t="n">
-        <v>921</v>
+        <v>883</v>
       </c>
       <c r="K9" t="n">
-        <v>859</v>
+        <v>826</v>
       </c>
       <c r="L9" t="n">
-        <v>922</v>
+        <v>857.1</v>
       </c>
     </row>
     <row r="10">
@@ -775,37 +775,37 @@
         <v>17</v>
       </c>
       <c r="B10" t="n">
-        <v>809</v>
+        <v>909</v>
       </c>
       <c r="C10" t="n">
-        <v>951</v>
+        <v>1064</v>
       </c>
       <c r="D10" t="n">
-        <v>986</v>
+        <v>728</v>
       </c>
       <c r="E10" t="n">
-        <v>771</v>
+        <v>971</v>
       </c>
       <c r="F10" t="n">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="G10" t="n">
-        <v>762</v>
+        <v>972</v>
       </c>
       <c r="H10" t="n">
-        <v>760</v>
+        <v>906</v>
       </c>
       <c r="I10" t="n">
-        <v>1015</v>
+        <v>793</v>
       </c>
       <c r="J10" t="n">
-        <v>715</v>
+        <v>839</v>
       </c>
       <c r="K10" t="n">
-        <v>954</v>
+        <v>1028</v>
       </c>
       <c r="L10" t="n">
-        <v>848.4</v>
+        <v>897</v>
       </c>
     </row>
     <row r="11">
@@ -813,37 +813,37 @@
         <v>18</v>
       </c>
       <c r="B11" t="n">
-        <v>818</v>
+        <v>871</v>
       </c>
       <c r="C11" t="n">
-        <v>845</v>
+        <v>785</v>
       </c>
       <c r="D11" t="n">
-        <v>834</v>
+        <v>911</v>
       </c>
       <c r="E11" t="n">
-        <v>899</v>
+        <v>926</v>
       </c>
       <c r="F11" t="n">
-        <v>954</v>
+        <v>880</v>
       </c>
       <c r="G11" t="n">
-        <v>991</v>
+        <v>853</v>
       </c>
       <c r="H11" t="n">
-        <v>917</v>
+        <v>775</v>
       </c>
       <c r="I11" t="n">
-        <v>925</v>
+        <v>919</v>
       </c>
       <c r="J11" t="n">
-        <v>920</v>
+        <v>892</v>
       </c>
       <c r="K11" t="n">
-        <v>855</v>
+        <v>1042</v>
       </c>
       <c r="L11" t="n">
-        <v>895.8</v>
+        <v>885.4</v>
       </c>
     </row>
     <row r="12">
@@ -851,37 +851,37 @@
         <v>19</v>
       </c>
       <c r="B12" t="n">
-        <v>1041</v>
+        <v>1277</v>
       </c>
       <c r="C12" t="n">
-        <v>772</v>
+        <v>1067</v>
       </c>
       <c r="D12" t="n">
-        <v>926</v>
+        <v>910</v>
       </c>
       <c r="E12" t="n">
-        <v>1085</v>
+        <v>992</v>
       </c>
       <c r="F12" t="n">
-        <v>866</v>
+        <v>1019</v>
       </c>
       <c r="G12" t="n">
-        <v>960</v>
+        <v>800</v>
       </c>
       <c r="H12" t="n">
-        <v>774</v>
+        <v>899</v>
       </c>
       <c r="I12" t="n">
-        <v>964</v>
+        <v>967</v>
       </c>
       <c r="J12" t="n">
-        <v>973</v>
+        <v>1025</v>
       </c>
       <c r="K12" t="n">
-        <v>1089</v>
+        <v>1064</v>
       </c>
       <c r="L12" t="n">
-        <v>945</v>
+        <v>1002</v>
       </c>
     </row>
     <row r="13">
@@ -889,37 +889,37 @@
         <v>2</v>
       </c>
       <c r="B13" t="n">
-        <v>1011</v>
+        <v>780</v>
       </c>
       <c r="C13" t="n">
-        <v>912</v>
+        <v>739</v>
       </c>
       <c r="D13" t="n">
-        <v>846</v>
+        <v>913</v>
       </c>
       <c r="E13" t="n">
-        <v>914</v>
+        <v>1004</v>
       </c>
       <c r="F13" t="n">
-        <v>718</v>
+        <v>899</v>
       </c>
       <c r="G13" t="n">
-        <v>844</v>
+        <v>913</v>
       </c>
       <c r="H13" t="n">
-        <v>811</v>
+        <v>882</v>
       </c>
       <c r="I13" t="n">
-        <v>762</v>
+        <v>805</v>
       </c>
       <c r="J13" t="n">
-        <v>701</v>
+        <v>776</v>
       </c>
       <c r="K13" t="n">
-        <v>710</v>
+        <v>853</v>
       </c>
       <c r="L13" t="n">
-        <v>822.9</v>
+        <v>856.4</v>
       </c>
     </row>
     <row r="14">
@@ -927,37 +927,37 @@
         <v>20</v>
       </c>
       <c r="B14" t="n">
-        <v>904</v>
+        <v>846</v>
       </c>
       <c r="C14" t="n">
-        <v>926</v>
+        <v>699</v>
       </c>
       <c r="D14" t="n">
-        <v>898</v>
+        <v>881</v>
       </c>
       <c r="E14" t="n">
-        <v>946</v>
+        <v>944</v>
       </c>
       <c r="F14" t="n">
-        <v>867</v>
+        <v>751</v>
       </c>
       <c r="G14" t="n">
-        <v>823</v>
+        <v>961</v>
       </c>
       <c r="H14" t="n">
-        <v>872</v>
+        <v>813</v>
       </c>
       <c r="I14" t="n">
-        <v>779</v>
+        <v>777</v>
       </c>
       <c r="J14" t="n">
-        <v>898</v>
+        <v>1052</v>
       </c>
       <c r="K14" t="n">
-        <v>814</v>
+        <v>919</v>
       </c>
       <c r="L14" t="n">
-        <v>872.7</v>
+        <v>864.3</v>
       </c>
     </row>
     <row r="15">
@@ -965,37 +965,37 @@
         <v>21</v>
       </c>
       <c r="B15" t="n">
-        <v>796</v>
+        <v>929</v>
       </c>
       <c r="C15" t="n">
+        <v>752</v>
+      </c>
+      <c r="D15" t="n">
+        <v>1089</v>
+      </c>
+      <c r="E15" t="n">
+        <v>914</v>
+      </c>
+      <c r="F15" t="n">
+        <v>754</v>
+      </c>
+      <c r="G15" t="n">
+        <v>858</v>
+      </c>
+      <c r="H15" t="n">
+        <v>709</v>
+      </c>
+      <c r="I15" t="n">
+        <v>803</v>
+      </c>
+      <c r="J15" t="n">
+        <v>882</v>
+      </c>
+      <c r="K15" t="n">
         <v>956</v>
       </c>
-      <c r="D15" t="n">
-        <v>856</v>
-      </c>
-      <c r="E15" t="n">
-        <v>838</v>
-      </c>
-      <c r="F15" t="n">
-        <v>841</v>
-      </c>
-      <c r="G15" t="n">
-        <v>1099</v>
-      </c>
-      <c r="H15" t="n">
-        <v>855</v>
-      </c>
-      <c r="I15" t="n">
-        <v>935</v>
-      </c>
-      <c r="J15" t="n">
-        <v>865</v>
-      </c>
-      <c r="K15" t="n">
-        <v>1037</v>
-      </c>
       <c r="L15" t="n">
-        <v>907.8</v>
+        <v>864.6</v>
       </c>
     </row>
     <row r="16">
@@ -1003,37 +1003,37 @@
         <v>22</v>
       </c>
       <c r="B16" t="n">
-        <v>943</v>
+        <v>954</v>
       </c>
       <c r="C16" t="n">
-        <v>962</v>
+        <v>1005</v>
       </c>
       <c r="D16" t="n">
-        <v>814</v>
+        <v>1077</v>
       </c>
       <c r="E16" t="n">
-        <v>886</v>
+        <v>1075</v>
       </c>
       <c r="F16" t="n">
-        <v>1025</v>
+        <v>866</v>
       </c>
       <c r="G16" t="n">
-        <v>921</v>
+        <v>993</v>
       </c>
       <c r="H16" t="n">
-        <v>847</v>
+        <v>881</v>
       </c>
       <c r="I16" t="n">
-        <v>837</v>
+        <v>827</v>
       </c>
       <c r="J16" t="n">
-        <v>901</v>
+        <v>852</v>
       </c>
       <c r="K16" t="n">
-        <v>1101</v>
+        <v>984</v>
       </c>
       <c r="L16" t="n">
-        <v>923.7</v>
+        <v>951.4</v>
       </c>
     </row>
     <row r="17">
@@ -1041,37 +1041,37 @@
         <v>23</v>
       </c>
       <c r="B17" t="n">
-        <v>1030</v>
+        <v>945</v>
       </c>
       <c r="C17" t="n">
-        <v>901</v>
+        <v>888</v>
       </c>
       <c r="D17" t="n">
-        <v>967</v>
+        <v>891</v>
       </c>
       <c r="E17" t="n">
-        <v>856</v>
+        <v>1088</v>
       </c>
       <c r="F17" t="n">
-        <v>889</v>
+        <v>960</v>
       </c>
       <c r="G17" t="n">
-        <v>1061</v>
+        <v>866</v>
       </c>
       <c r="H17" t="n">
-        <v>991</v>
+        <v>876</v>
       </c>
       <c r="I17" t="n">
-        <v>1021</v>
+        <v>982</v>
       </c>
       <c r="J17" t="n">
-        <v>1059</v>
+        <v>885</v>
       </c>
       <c r="K17" t="n">
-        <v>831</v>
+        <v>814</v>
       </c>
       <c r="L17" t="n">
-        <v>960.6</v>
+        <v>919.5</v>
       </c>
     </row>
     <row r="18">
@@ -1079,37 +1079,37 @@
         <v>24</v>
       </c>
       <c r="B18" t="n">
-        <v>867</v>
+        <v>848</v>
       </c>
       <c r="C18" t="n">
-        <v>845</v>
+        <v>869</v>
       </c>
       <c r="D18" t="n">
-        <v>805</v>
+        <v>1162</v>
       </c>
       <c r="E18" t="n">
-        <v>919</v>
+        <v>814</v>
       </c>
       <c r="F18" t="n">
-        <v>872</v>
+        <v>792</v>
       </c>
       <c r="G18" t="n">
-        <v>897</v>
+        <v>1005</v>
       </c>
       <c r="H18" t="n">
-        <v>926</v>
+        <v>817</v>
       </c>
       <c r="I18" t="n">
-        <v>858</v>
+        <v>1089</v>
       </c>
       <c r="J18" t="n">
-        <v>868</v>
+        <v>847</v>
       </c>
       <c r="K18" t="n">
-        <v>965</v>
+        <v>894</v>
       </c>
       <c r="L18" t="n">
-        <v>882.2</v>
+        <v>913.7</v>
       </c>
     </row>
     <row r="19">
@@ -1117,37 +1117,37 @@
         <v>25</v>
       </c>
       <c r="B19" t="n">
-        <v>925</v>
+        <v>823</v>
       </c>
       <c r="C19" t="n">
-        <v>1031</v>
+        <v>865</v>
       </c>
       <c r="D19" t="n">
-        <v>743</v>
+        <v>773</v>
       </c>
       <c r="E19" t="n">
-        <v>867</v>
+        <v>820</v>
       </c>
       <c r="F19" t="n">
-        <v>820</v>
+        <v>922</v>
       </c>
       <c r="G19" t="n">
-        <v>818</v>
+        <v>926</v>
       </c>
       <c r="H19" t="n">
-        <v>734</v>
+        <v>946</v>
       </c>
       <c r="I19" t="n">
-        <v>994</v>
+        <v>1059</v>
       </c>
       <c r="J19" t="n">
-        <v>893</v>
+        <v>1018</v>
       </c>
       <c r="K19" t="n">
-        <v>786</v>
+        <v>947</v>
       </c>
       <c r="L19" t="n">
-        <v>861.1</v>
+        <v>909.9</v>
       </c>
     </row>
     <row r="20">
@@ -1155,37 +1155,37 @@
         <v>26</v>
       </c>
       <c r="B20" t="n">
-        <v>876</v>
+        <v>1032</v>
       </c>
       <c r="C20" t="n">
-        <v>1116</v>
+        <v>988</v>
       </c>
       <c r="D20" t="n">
-        <v>892</v>
+        <v>855</v>
       </c>
       <c r="E20" t="n">
-        <v>1081</v>
+        <v>903</v>
       </c>
       <c r="F20" t="n">
-        <v>1063</v>
+        <v>938</v>
       </c>
       <c r="G20" t="n">
-        <v>904</v>
+        <v>992</v>
       </c>
       <c r="H20" t="n">
-        <v>907</v>
+        <v>890</v>
       </c>
       <c r="I20" t="n">
-        <v>951</v>
+        <v>1028</v>
       </c>
       <c r="J20" t="n">
-        <v>878</v>
+        <v>1046</v>
       </c>
       <c r="K20" t="n">
-        <v>1002</v>
+        <v>825</v>
       </c>
       <c r="L20" t="n">
-        <v>967</v>
+        <v>949.7</v>
       </c>
     </row>
     <row r="21">
@@ -1193,37 +1193,37 @@
         <v>27</v>
       </c>
       <c r="B21" t="n">
-        <v>891</v>
+        <v>937</v>
       </c>
       <c r="C21" t="n">
-        <v>920</v>
+        <v>994</v>
       </c>
       <c r="D21" t="n">
-        <v>973</v>
+        <v>759</v>
       </c>
       <c r="E21" t="n">
-        <v>1048</v>
+        <v>897</v>
       </c>
       <c r="F21" t="n">
-        <v>905</v>
+        <v>840</v>
       </c>
       <c r="G21" t="n">
-        <v>962</v>
+        <v>1030</v>
       </c>
       <c r="H21" t="n">
-        <v>819</v>
+        <v>787</v>
       </c>
       <c r="I21" t="n">
-        <v>1075</v>
+        <v>909</v>
       </c>
       <c r="J21" t="n">
-        <v>985</v>
+        <v>979</v>
       </c>
       <c r="K21" t="n">
-        <v>965</v>
+        <v>996</v>
       </c>
       <c r="L21" t="n">
-        <v>954.3</v>
+        <v>912.8</v>
       </c>
     </row>
     <row r="22">
@@ -1231,37 +1231,37 @@
         <v>28</v>
       </c>
       <c r="B22" t="n">
-        <v>788</v>
+        <v>1071</v>
       </c>
       <c r="C22" t="n">
-        <v>858</v>
+        <v>923</v>
       </c>
       <c r="D22" t="n">
-        <v>842</v>
+        <v>950</v>
       </c>
       <c r="E22" t="n">
-        <v>827</v>
+        <v>826</v>
       </c>
       <c r="F22" t="n">
-        <v>788</v>
+        <v>866</v>
       </c>
       <c r="G22" t="n">
-        <v>880</v>
+        <v>818</v>
       </c>
       <c r="H22" t="n">
-        <v>823</v>
+        <v>743</v>
       </c>
       <c r="I22" t="n">
-        <v>1081</v>
+        <v>840</v>
       </c>
       <c r="J22" t="n">
-        <v>822</v>
+        <v>905</v>
       </c>
       <c r="K22" t="n">
-        <v>860</v>
+        <v>830</v>
       </c>
       <c r="L22" t="n">
-        <v>856.9</v>
+        <v>877.2</v>
       </c>
     </row>
     <row r="23">
@@ -1269,37 +1269,37 @@
         <v>29</v>
       </c>
       <c r="B23" t="n">
-        <v>1033</v>
+        <v>1076</v>
       </c>
       <c r="C23" t="n">
-        <v>1077</v>
+        <v>1125</v>
       </c>
       <c r="D23" t="n">
-        <v>1132</v>
+        <v>1000</v>
       </c>
       <c r="E23" t="n">
-        <v>1052</v>
+        <v>941</v>
       </c>
       <c r="F23" t="n">
         <v>1016</v>
       </c>
       <c r="G23" t="n">
-        <v>1164</v>
+        <v>1030</v>
       </c>
       <c r="H23" t="n">
-        <v>1047</v>
+        <v>1026</v>
       </c>
       <c r="I23" t="n">
-        <v>1106</v>
+        <v>975</v>
       </c>
       <c r="J23" t="n">
-        <v>1088</v>
+        <v>1066</v>
       </c>
       <c r="K23" t="n">
-        <v>1116</v>
+        <v>1079</v>
       </c>
       <c r="L23" t="n">
-        <v>1083.1</v>
+        <v>1033.4</v>
       </c>
     </row>
     <row r="24">
@@ -1307,37 +1307,37 @@
         <v>3</v>
       </c>
       <c r="B24" t="n">
-        <v>837</v>
+        <v>982</v>
       </c>
       <c r="C24" t="n">
-        <v>908</v>
+        <v>1025</v>
       </c>
       <c r="D24" t="n">
-        <v>925</v>
+        <v>906</v>
       </c>
       <c r="E24" t="n">
-        <v>1006</v>
+        <v>988</v>
       </c>
       <c r="F24" t="n">
-        <v>1052</v>
+        <v>1084</v>
       </c>
       <c r="G24" t="n">
-        <v>1034</v>
+        <v>1048</v>
       </c>
       <c r="H24" t="n">
-        <v>886</v>
+        <v>1085</v>
       </c>
       <c r="I24" t="n">
-        <v>1085</v>
+        <v>898</v>
       </c>
       <c r="J24" t="n">
-        <v>998</v>
+        <v>1156</v>
       </c>
       <c r="K24" t="n">
-        <v>1111</v>
+        <v>788</v>
       </c>
       <c r="L24" t="n">
-        <v>984.2</v>
+        <v>996</v>
       </c>
     </row>
     <row r="25">
@@ -1345,37 +1345,37 @@
         <v>30</v>
       </c>
       <c r="B25" t="n">
-        <v>868</v>
+        <v>971</v>
       </c>
       <c r="C25" t="n">
-        <v>853</v>
+        <v>978</v>
       </c>
       <c r="D25" t="n">
+        <v>941</v>
+      </c>
+      <c r="E25" t="n">
+        <v>1024</v>
+      </c>
+      <c r="F25" t="n">
+        <v>963</v>
+      </c>
+      <c r="G25" t="n">
+        <v>879</v>
+      </c>
+      <c r="H25" t="n">
+        <v>904</v>
+      </c>
+      <c r="I25" t="n">
+        <v>1084</v>
+      </c>
+      <c r="J25" t="n">
+        <v>1004</v>
+      </c>
+      <c r="K25" t="n">
         <v>884</v>
       </c>
-      <c r="E25" t="n">
-        <v>930</v>
-      </c>
-      <c r="F25" t="n">
-        <v>867</v>
-      </c>
-      <c r="G25" t="n">
-        <v>863</v>
-      </c>
-      <c r="H25" t="n">
-        <v>1026</v>
-      </c>
-      <c r="I25" t="n">
-        <v>942</v>
-      </c>
-      <c r="J25" t="n">
-        <v>888</v>
-      </c>
-      <c r="K25" t="n">
-        <v>904</v>
-      </c>
       <c r="L25" t="n">
-        <v>902.5</v>
+        <v>963.2</v>
       </c>
     </row>
     <row r="26">
@@ -1383,37 +1383,37 @@
         <v>31</v>
       </c>
       <c r="B26" t="n">
-        <v>881</v>
+        <v>800</v>
       </c>
       <c r="C26" t="n">
-        <v>951</v>
+        <v>782</v>
       </c>
       <c r="D26" t="n">
-        <v>861</v>
+        <v>783</v>
       </c>
       <c r="E26" t="n">
-        <v>753</v>
+        <v>1028</v>
       </c>
       <c r="F26" t="n">
-        <v>849</v>
+        <v>950</v>
       </c>
       <c r="G26" t="n">
-        <v>953</v>
+        <v>860</v>
       </c>
       <c r="H26" t="n">
-        <v>857</v>
+        <v>1027</v>
       </c>
       <c r="I26" t="n">
-        <v>944</v>
+        <v>783</v>
       </c>
       <c r="J26" t="n">
-        <v>1038</v>
+        <v>777</v>
       </c>
       <c r="K26" t="n">
-        <v>973</v>
+        <v>1003</v>
       </c>
       <c r="L26" t="n">
-        <v>906</v>
+        <v>879.3</v>
       </c>
     </row>
     <row r="27">
@@ -1421,37 +1421,37 @@
         <v>32</v>
       </c>
       <c r="B27" t="n">
-        <v>1091</v>
+        <v>1068</v>
       </c>
       <c r="C27" t="n">
-        <v>1087</v>
+        <v>1121</v>
       </c>
       <c r="D27" t="n">
-        <v>821</v>
+        <v>1015</v>
       </c>
       <c r="E27" t="n">
-        <v>1004</v>
+        <v>1023</v>
       </c>
       <c r="F27" t="n">
-        <v>1010</v>
+        <v>978</v>
       </c>
       <c r="G27" t="n">
-        <v>1064</v>
+        <v>926</v>
       </c>
       <c r="H27" t="n">
-        <v>1018</v>
+        <v>809</v>
       </c>
       <c r="I27" t="n">
-        <v>850</v>
+        <v>1148</v>
       </c>
       <c r="J27" t="n">
-        <v>805</v>
+        <v>1021</v>
       </c>
       <c r="K27" t="n">
-        <v>835</v>
+        <v>992</v>
       </c>
       <c r="L27" t="n">
-        <v>958.5</v>
+        <v>1010.1</v>
       </c>
     </row>
     <row r="28">
@@ -1459,37 +1459,37 @@
         <v>33</v>
       </c>
       <c r="B28" t="n">
-        <v>944</v>
+        <v>998</v>
       </c>
       <c r="C28" t="n">
-        <v>930</v>
+        <v>804</v>
       </c>
       <c r="D28" t="n">
-        <v>930</v>
+        <v>989</v>
       </c>
       <c r="E28" t="n">
-        <v>857</v>
+        <v>910</v>
       </c>
       <c r="F28" t="n">
-        <v>871</v>
+        <v>945</v>
       </c>
       <c r="G28" t="n">
-        <v>1076</v>
+        <v>799</v>
       </c>
       <c r="H28" t="n">
-        <v>929</v>
+        <v>1005</v>
       </c>
       <c r="I28" t="n">
-        <v>913</v>
+        <v>1025</v>
       </c>
       <c r="J28" t="n">
-        <v>910</v>
+        <v>777</v>
       </c>
       <c r="K28" t="n">
-        <v>871</v>
+        <v>863</v>
       </c>
       <c r="L28" t="n">
-        <v>923.1</v>
+        <v>911.5</v>
       </c>
     </row>
     <row r="29">
@@ -1497,37 +1497,37 @@
         <v>34</v>
       </c>
       <c r="B29" t="n">
-        <v>901</v>
+        <v>844</v>
       </c>
       <c r="C29" t="n">
-        <v>801</v>
+        <v>782</v>
       </c>
       <c r="D29" t="n">
-        <v>880</v>
+        <v>961</v>
       </c>
       <c r="E29" t="n">
-        <v>906</v>
+        <v>930</v>
       </c>
       <c r="F29" t="n">
-        <v>755</v>
+        <v>1016</v>
       </c>
       <c r="G29" t="n">
-        <v>755</v>
+        <v>895</v>
       </c>
       <c r="H29" t="n">
-        <v>936</v>
+        <v>997</v>
       </c>
       <c r="I29" t="n">
-        <v>918</v>
+        <v>957</v>
       </c>
       <c r="J29" t="n">
-        <v>966</v>
+        <v>881</v>
       </c>
       <c r="K29" t="n">
-        <v>765</v>
+        <v>1084</v>
       </c>
       <c r="L29" t="n">
-        <v>858.3</v>
+        <v>934.7</v>
       </c>
     </row>
     <row r="30">
@@ -1535,37 +1535,37 @@
         <v>35</v>
       </c>
       <c r="B30" t="n">
-        <v>969</v>
+        <v>949</v>
       </c>
       <c r="C30" t="n">
-        <v>919</v>
+        <v>931</v>
       </c>
       <c r="D30" t="n">
+        <v>861</v>
+      </c>
+      <c r="E30" t="n">
+        <v>752</v>
+      </c>
+      <c r="F30" t="n">
+        <v>1006</v>
+      </c>
+      <c r="G30" t="n">
+        <v>1001</v>
+      </c>
+      <c r="H30" t="n">
+        <v>916</v>
+      </c>
+      <c r="I30" t="n">
+        <v>993</v>
+      </c>
+      <c r="J30" t="n">
         <v>974</v>
       </c>
-      <c r="E30" t="n">
-        <v>968</v>
-      </c>
-      <c r="F30" t="n">
-        <v>1160</v>
-      </c>
-      <c r="G30" t="n">
-        <v>963</v>
-      </c>
-      <c r="H30" t="n">
-        <v>1073</v>
-      </c>
-      <c r="I30" t="n">
-        <v>952</v>
-      </c>
-      <c r="J30" t="n">
-        <v>879</v>
-      </c>
       <c r="K30" t="n">
-        <v>962</v>
+        <v>957</v>
       </c>
       <c r="L30" t="n">
-        <v>981.9</v>
+        <v>934</v>
       </c>
     </row>
     <row r="31">
@@ -1573,37 +1573,37 @@
         <v>36</v>
       </c>
       <c r="B31" t="n">
-        <v>886</v>
+        <v>862</v>
       </c>
       <c r="C31" t="n">
-        <v>722</v>
+        <v>874</v>
       </c>
       <c r="D31" t="n">
-        <v>839</v>
+        <v>773</v>
       </c>
       <c r="E31" t="n">
-        <v>946</v>
+        <v>1026</v>
       </c>
       <c r="F31" t="n">
-        <v>1006</v>
+        <v>964</v>
       </c>
       <c r="G31" t="n">
-        <v>739</v>
+        <v>1012</v>
       </c>
       <c r="H31" t="n">
-        <v>1026</v>
+        <v>972</v>
       </c>
       <c r="I31" t="n">
-        <v>978</v>
+        <v>786</v>
       </c>
       <c r="J31" t="n">
-        <v>848</v>
+        <v>972</v>
       </c>
       <c r="K31" t="n">
-        <v>873</v>
+        <v>900</v>
       </c>
       <c r="L31" t="n">
-        <v>886.3</v>
+        <v>914.1</v>
       </c>
     </row>
     <row r="32">
@@ -1611,37 +1611,37 @@
         <v>37</v>
       </c>
       <c r="B32" t="n">
-        <v>1162</v>
+        <v>918</v>
       </c>
       <c r="C32" t="n">
-        <v>997</v>
+        <v>838</v>
       </c>
       <c r="D32" t="n">
-        <v>896</v>
+        <v>980</v>
       </c>
       <c r="E32" t="n">
-        <v>760</v>
+        <v>857</v>
       </c>
       <c r="F32" t="n">
-        <v>1002</v>
+        <v>910</v>
       </c>
       <c r="G32" t="n">
-        <v>876</v>
+        <v>889</v>
       </c>
       <c r="H32" t="n">
-        <v>941</v>
+        <v>967</v>
       </c>
       <c r="I32" t="n">
-        <v>870</v>
+        <v>893</v>
       </c>
       <c r="J32" t="n">
-        <v>801</v>
+        <v>890</v>
       </c>
       <c r="K32" t="n">
-        <v>872</v>
+        <v>826</v>
       </c>
       <c r="L32" t="n">
-        <v>917.7</v>
+        <v>896.8</v>
       </c>
     </row>
     <row r="33">
@@ -1649,37 +1649,37 @@
         <v>38</v>
       </c>
       <c r="B33" t="n">
-        <v>885</v>
+        <v>967</v>
       </c>
       <c r="C33" t="n">
-        <v>958</v>
+        <v>730</v>
       </c>
       <c r="D33" t="n">
-        <v>800</v>
+        <v>874</v>
       </c>
       <c r="E33" t="n">
-        <v>824</v>
+        <v>766</v>
       </c>
       <c r="F33" t="n">
-        <v>965</v>
+        <v>820</v>
       </c>
       <c r="G33" t="n">
-        <v>745</v>
+        <v>861</v>
       </c>
       <c r="H33" t="n">
-        <v>814</v>
+        <v>809</v>
       </c>
       <c r="I33" t="n">
-        <v>934</v>
+        <v>856</v>
       </c>
       <c r="J33" t="n">
-        <v>834</v>
+        <v>827</v>
       </c>
       <c r="K33" t="n">
-        <v>898</v>
+        <v>870</v>
       </c>
       <c r="L33" t="n">
-        <v>865.7</v>
+        <v>838</v>
       </c>
     </row>
     <row r="34">
@@ -1687,37 +1687,37 @@
         <v>39</v>
       </c>
       <c r="B34" t="n">
-        <v>918</v>
+        <v>849</v>
       </c>
       <c r="C34" t="n">
-        <v>1021</v>
+        <v>842</v>
       </c>
       <c r="D34" t="n">
-        <v>926</v>
+        <v>841</v>
       </c>
       <c r="E34" t="n">
-        <v>977</v>
+        <v>859</v>
       </c>
       <c r="F34" t="n">
-        <v>948</v>
+        <v>858</v>
       </c>
       <c r="G34" t="n">
-        <v>822</v>
+        <v>771</v>
       </c>
       <c r="H34" t="n">
-        <v>911</v>
+        <v>836</v>
       </c>
       <c r="I34" t="n">
-        <v>935</v>
+        <v>912</v>
       </c>
       <c r="J34" t="n">
-        <v>855</v>
+        <v>843</v>
       </c>
       <c r="K34" t="n">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="L34" t="n">
-        <v>907.5</v>
+        <v>837.2</v>
       </c>
     </row>
     <row r="35">
@@ -1725,37 +1725,37 @@
         <v>4</v>
       </c>
       <c r="B35" t="n">
-        <v>908</v>
+        <v>941</v>
       </c>
       <c r="C35" t="n">
-        <v>841</v>
+        <v>915</v>
       </c>
       <c r="D35" t="n">
-        <v>853</v>
+        <v>823</v>
       </c>
       <c r="E35" t="n">
-        <v>980</v>
+        <v>827</v>
       </c>
       <c r="F35" t="n">
-        <v>875</v>
+        <v>776</v>
       </c>
       <c r="G35" t="n">
-        <v>821</v>
+        <v>829</v>
       </c>
       <c r="H35" t="n">
-        <v>947</v>
+        <v>1017</v>
       </c>
       <c r="I35" t="n">
-        <v>789</v>
+        <v>892</v>
       </c>
       <c r="J35" t="n">
-        <v>807</v>
+        <v>783</v>
       </c>
       <c r="K35" t="n">
-        <v>804</v>
+        <v>868</v>
       </c>
       <c r="L35" t="n">
-        <v>862.5</v>
+        <v>867.1</v>
       </c>
     </row>
     <row r="36">
@@ -1763,37 +1763,37 @@
         <v>40</v>
       </c>
       <c r="B36" t="n">
-        <v>1007</v>
+        <v>1127</v>
       </c>
       <c r="C36" t="n">
-        <v>1005</v>
+        <v>861</v>
       </c>
       <c r="D36" t="n">
-        <v>1020</v>
+        <v>878</v>
       </c>
       <c r="E36" t="n">
-        <v>975</v>
+        <v>1025</v>
       </c>
       <c r="F36" t="n">
-        <v>1050</v>
+        <v>1060</v>
       </c>
       <c r="G36" t="n">
-        <v>872</v>
+        <v>996</v>
       </c>
       <c r="H36" t="n">
-        <v>1104</v>
+        <v>967</v>
       </c>
       <c r="I36" t="n">
-        <v>928</v>
+        <v>972</v>
       </c>
       <c r="J36" t="n">
-        <v>1043</v>
+        <v>1137</v>
       </c>
       <c r="K36" t="n">
-        <v>1043</v>
+        <v>1001</v>
       </c>
       <c r="L36" t="n">
-        <v>1004.7</v>
+        <v>1002.4</v>
       </c>
     </row>
     <row r="37">
@@ -1801,37 +1801,37 @@
         <v>41</v>
       </c>
       <c r="B37" t="n">
-        <v>734</v>
+        <v>792</v>
       </c>
       <c r="C37" t="n">
+        <v>830</v>
+      </c>
+      <c r="D37" t="n">
+        <v>805</v>
+      </c>
+      <c r="E37" t="n">
+        <v>749</v>
+      </c>
+      <c r="F37" t="n">
+        <v>733</v>
+      </c>
+      <c r="G37" t="n">
+        <v>823</v>
+      </c>
+      <c r="H37" t="n">
+        <v>822</v>
+      </c>
+      <c r="I37" t="n">
         <v>785</v>
       </c>
-      <c r="D37" t="n">
-        <v>857</v>
-      </c>
-      <c r="E37" t="n">
-        <v>718</v>
-      </c>
-      <c r="F37" t="n">
-        <v>712</v>
-      </c>
-      <c r="G37" t="n">
-        <v>1010</v>
-      </c>
-      <c r="H37" t="n">
-        <v>743</v>
-      </c>
-      <c r="I37" t="n">
-        <v>885</v>
-      </c>
       <c r="J37" t="n">
-        <v>785</v>
+        <v>773</v>
       </c>
       <c r="K37" t="n">
-        <v>907</v>
+        <v>739</v>
       </c>
       <c r="L37" t="n">
-        <v>813.6</v>
+        <v>785.1</v>
       </c>
     </row>
     <row r="38">
@@ -1839,37 +1839,37 @@
         <v>42</v>
       </c>
       <c r="B38" t="n">
-        <v>818</v>
+        <v>992</v>
       </c>
       <c r="C38" t="n">
-        <v>897</v>
+        <v>805</v>
       </c>
       <c r="D38" t="n">
-        <v>1023</v>
+        <v>846</v>
       </c>
       <c r="E38" t="n">
-        <v>817</v>
+        <v>984</v>
       </c>
       <c r="F38" t="n">
-        <v>995</v>
+        <v>904</v>
       </c>
       <c r="G38" t="n">
-        <v>972</v>
+        <v>1046</v>
       </c>
       <c r="H38" t="n">
-        <v>958</v>
+        <v>761</v>
       </c>
       <c r="I38" t="n">
-        <v>807</v>
+        <v>1016</v>
       </c>
       <c r="J38" t="n">
-        <v>1052</v>
+        <v>956</v>
       </c>
       <c r="K38" t="n">
-        <v>1027</v>
+        <v>967</v>
       </c>
       <c r="L38" t="n">
-        <v>936.6</v>
+        <v>927.7</v>
       </c>
     </row>
     <row r="39">
@@ -1877,37 +1877,37 @@
         <v>43</v>
       </c>
       <c r="B39" t="n">
-        <v>721</v>
+        <v>806</v>
       </c>
       <c r="C39" t="n">
-        <v>768</v>
+        <v>886</v>
       </c>
       <c r="D39" t="n">
-        <v>771</v>
+        <v>723</v>
       </c>
       <c r="E39" t="n">
-        <v>808</v>
+        <v>876</v>
       </c>
       <c r="F39" t="n">
-        <v>927</v>
+        <v>747</v>
       </c>
       <c r="G39" t="n">
-        <v>748</v>
+        <v>904</v>
       </c>
       <c r="H39" t="n">
-        <v>874</v>
+        <v>1039</v>
       </c>
       <c r="I39" t="n">
-        <v>916</v>
+        <v>871</v>
       </c>
       <c r="J39" t="n">
-        <v>754</v>
+        <v>964</v>
       </c>
       <c r="K39" t="n">
-        <v>1016</v>
+        <v>934</v>
       </c>
       <c r="L39" t="n">
-        <v>830.3</v>
+        <v>875</v>
       </c>
     </row>
     <row r="40">
@@ -1915,37 +1915,37 @@
         <v>44</v>
       </c>
       <c r="B40" t="n">
-        <v>816</v>
+        <v>840</v>
       </c>
       <c r="C40" t="n">
-        <v>878</v>
+        <v>841</v>
       </c>
       <c r="D40" t="n">
-        <v>937</v>
+        <v>876</v>
       </c>
       <c r="E40" t="n">
-        <v>819</v>
+        <v>746</v>
       </c>
       <c r="F40" t="n">
-        <v>901</v>
+        <v>1026</v>
       </c>
       <c r="G40" t="n">
-        <v>991</v>
+        <v>822</v>
       </c>
       <c r="H40" t="n">
-        <v>1093</v>
+        <v>1065</v>
       </c>
       <c r="I40" t="n">
-        <v>989</v>
+        <v>868</v>
       </c>
       <c r="J40" t="n">
-        <v>823</v>
+        <v>869</v>
       </c>
       <c r="K40" t="n">
-        <v>1077</v>
+        <v>934</v>
       </c>
       <c r="L40" t="n">
-        <v>932.4</v>
+        <v>888.7</v>
       </c>
     </row>
     <row r="41">
@@ -1953,37 +1953,37 @@
         <v>45</v>
       </c>
       <c r="B41" t="n">
-        <v>837</v>
+        <v>996</v>
       </c>
       <c r="C41" t="n">
-        <v>770</v>
+        <v>836</v>
       </c>
       <c r="D41" t="n">
-        <v>914</v>
+        <v>741</v>
       </c>
       <c r="E41" t="n">
-        <v>995</v>
+        <v>989</v>
       </c>
       <c r="F41" t="n">
-        <v>882</v>
+        <v>845</v>
       </c>
       <c r="G41" t="n">
-        <v>764</v>
+        <v>828</v>
       </c>
       <c r="H41" t="n">
-        <v>900</v>
+        <v>1087</v>
       </c>
       <c r="I41" t="n">
-        <v>973</v>
+        <v>820</v>
       </c>
       <c r="J41" t="n">
-        <v>870</v>
+        <v>811</v>
       </c>
       <c r="K41" t="n">
-        <v>860</v>
+        <v>877</v>
       </c>
       <c r="L41" t="n">
-        <v>876.5</v>
+        <v>883</v>
       </c>
     </row>
     <row r="42">
@@ -1994,34 +1994,34 @@
         <v>724</v>
       </c>
       <c r="C42" t="n">
-        <v>897</v>
+        <v>789</v>
       </c>
       <c r="D42" t="n">
-        <v>768</v>
+        <v>809</v>
       </c>
       <c r="E42" t="n">
-        <v>873</v>
+        <v>958</v>
       </c>
       <c r="F42" t="n">
-        <v>883</v>
+        <v>734</v>
       </c>
       <c r="G42" t="n">
-        <v>886</v>
+        <v>983</v>
       </c>
       <c r="H42" t="n">
-        <v>852</v>
+        <v>791</v>
       </c>
       <c r="I42" t="n">
-        <v>744</v>
+        <v>980</v>
       </c>
       <c r="J42" t="n">
-        <v>727</v>
+        <v>734</v>
       </c>
       <c r="K42" t="n">
-        <v>739</v>
+        <v>813</v>
       </c>
       <c r="L42" t="n">
-        <v>809.3</v>
+        <v>831.5</v>
       </c>
     </row>
     <row r="43">
@@ -2029,37 +2029,37 @@
         <v>47</v>
       </c>
       <c r="B43" t="n">
-        <v>730</v>
+        <v>736</v>
       </c>
       <c r="C43" t="n">
-        <v>921</v>
+        <v>884</v>
       </c>
       <c r="D43" t="n">
-        <v>987</v>
+        <v>1072</v>
       </c>
       <c r="E43" t="n">
+        <v>890</v>
+      </c>
+      <c r="F43" t="n">
+        <v>957</v>
+      </c>
+      <c r="G43" t="n">
         <v>992</v>
       </c>
-      <c r="F43" t="n">
-        <v>784</v>
-      </c>
-      <c r="G43" t="n">
-        <v>815</v>
-      </c>
       <c r="H43" t="n">
-        <v>896</v>
+        <v>956</v>
       </c>
       <c r="I43" t="n">
-        <v>920</v>
+        <v>723</v>
       </c>
       <c r="J43" t="n">
-        <v>825</v>
+        <v>1033</v>
       </c>
       <c r="K43" t="n">
-        <v>925</v>
+        <v>1047</v>
       </c>
       <c r="L43" t="n">
-        <v>879.5</v>
+        <v>929</v>
       </c>
     </row>
     <row r="44">
@@ -2067,37 +2067,37 @@
         <v>48</v>
       </c>
       <c r="B44" t="n">
+        <v>976</v>
+      </c>
+      <c r="C44" t="n">
+        <v>800</v>
+      </c>
+      <c r="D44" t="n">
+        <v>834</v>
+      </c>
+      <c r="E44" t="n">
+        <v>1007</v>
+      </c>
+      <c r="F44" t="n">
+        <v>1082</v>
+      </c>
+      <c r="G44" t="n">
+        <v>899</v>
+      </c>
+      <c r="H44" t="n">
+        <v>794</v>
+      </c>
+      <c r="I44" t="n">
         <v>786</v>
       </c>
-      <c r="C44" t="n">
-        <v>1002</v>
-      </c>
-      <c r="D44" t="n">
-        <v>775</v>
-      </c>
-      <c r="E44" t="n">
-        <v>944</v>
-      </c>
-      <c r="F44" t="n">
-        <v>821</v>
-      </c>
-      <c r="G44" t="n">
-        <v>929</v>
-      </c>
-      <c r="H44" t="n">
-        <v>950</v>
-      </c>
-      <c r="I44" t="n">
-        <v>947</v>
-      </c>
       <c r="J44" t="n">
-        <v>938</v>
+        <v>894</v>
       </c>
       <c r="K44" t="n">
-        <v>930</v>
+        <v>800</v>
       </c>
       <c r="L44" t="n">
-        <v>902.2</v>
+        <v>887.2</v>
       </c>
     </row>
     <row r="45">
@@ -2105,37 +2105,37 @@
         <v>49</v>
       </c>
       <c r="B45" t="n">
-        <v>740</v>
+        <v>912</v>
       </c>
       <c r="C45" t="n">
-        <v>995</v>
+        <v>966</v>
       </c>
       <c r="D45" t="n">
-        <v>945</v>
+        <v>967</v>
       </c>
       <c r="E45" t="n">
-        <v>839</v>
+        <v>955</v>
       </c>
       <c r="F45" t="n">
-        <v>996</v>
+        <v>986</v>
       </c>
       <c r="G45" t="n">
-        <v>848</v>
+        <v>936</v>
       </c>
       <c r="H45" t="n">
-        <v>845</v>
+        <v>889</v>
       </c>
       <c r="I45" t="n">
-        <v>760</v>
+        <v>1003</v>
       </c>
       <c r="J45" t="n">
-        <v>932</v>
+        <v>968</v>
       </c>
       <c r="K45" t="n">
-        <v>905</v>
+        <v>933</v>
       </c>
       <c r="L45" t="n">
-        <v>880.5</v>
+        <v>951.5</v>
       </c>
     </row>
     <row r="46">
@@ -2143,37 +2143,37 @@
         <v>5</v>
       </c>
       <c r="B46" t="n">
-        <v>907</v>
+        <v>878</v>
       </c>
       <c r="C46" t="n">
-        <v>1091</v>
+        <v>781</v>
       </c>
       <c r="D46" t="n">
-        <v>821</v>
+        <v>905</v>
       </c>
       <c r="E46" t="n">
-        <v>959</v>
+        <v>939</v>
       </c>
       <c r="F46" t="n">
-        <v>889</v>
+        <v>860</v>
       </c>
       <c r="G46" t="n">
-        <v>858</v>
+        <v>1035</v>
       </c>
       <c r="H46" t="n">
-        <v>1020</v>
+        <v>1040</v>
       </c>
       <c r="I46" t="n">
-        <v>1017</v>
+        <v>1023</v>
       </c>
       <c r="J46" t="n">
-        <v>846</v>
+        <v>864</v>
       </c>
       <c r="K46" t="n">
-        <v>812</v>
+        <v>1085</v>
       </c>
       <c r="L46" t="n">
-        <v>922</v>
+        <v>941</v>
       </c>
     </row>
     <row r="47">
@@ -2181,37 +2181,37 @@
         <v>50</v>
       </c>
       <c r="B47" t="n">
-        <v>833</v>
+        <v>873</v>
       </c>
       <c r="C47" t="n">
-        <v>1111</v>
+        <v>1104</v>
       </c>
       <c r="D47" t="n">
-        <v>1054</v>
+        <v>961</v>
       </c>
       <c r="E47" t="n">
-        <v>1042</v>
+        <v>1030</v>
       </c>
       <c r="F47" t="n">
-        <v>1105</v>
+        <v>990</v>
       </c>
       <c r="G47" t="n">
-        <v>896</v>
+        <v>1023</v>
       </c>
       <c r="H47" t="n">
-        <v>1082</v>
+        <v>1089</v>
       </c>
       <c r="I47" t="n">
-        <v>1044</v>
+        <v>883</v>
       </c>
       <c r="J47" t="n">
-        <v>1046</v>
+        <v>994</v>
       </c>
       <c r="K47" t="n">
-        <v>976</v>
+        <v>1057</v>
       </c>
       <c r="L47" t="n">
-        <v>1018.9</v>
+        <v>1000.4</v>
       </c>
     </row>
     <row r="48">
@@ -2219,37 +2219,37 @@
         <v>6</v>
       </c>
       <c r="B48" t="n">
-        <v>881</v>
+        <v>838</v>
       </c>
       <c r="C48" t="n">
-        <v>886</v>
+        <v>809</v>
       </c>
       <c r="D48" t="n">
-        <v>904</v>
+        <v>1029</v>
       </c>
       <c r="E48" t="n">
-        <v>915</v>
+        <v>888</v>
       </c>
       <c r="F48" t="n">
-        <v>989</v>
+        <v>934</v>
       </c>
       <c r="G48" t="n">
-        <v>800</v>
+        <v>738</v>
       </c>
       <c r="H48" t="n">
-        <v>767</v>
+        <v>778</v>
       </c>
       <c r="I48" t="n">
-        <v>827</v>
+        <v>786</v>
       </c>
       <c r="J48" t="n">
-        <v>949</v>
+        <v>818</v>
       </c>
       <c r="K48" t="n">
-        <v>876</v>
+        <v>863</v>
       </c>
       <c r="L48" t="n">
-        <v>879.4</v>
+        <v>848.1</v>
       </c>
     </row>
     <row r="49">
@@ -2257,37 +2257,37 @@
         <v>7</v>
       </c>
       <c r="B49" t="n">
-        <v>934</v>
+        <v>1015</v>
       </c>
       <c r="C49" t="n">
-        <v>855</v>
+        <v>852</v>
       </c>
       <c r="D49" t="n">
-        <v>979</v>
+        <v>895</v>
       </c>
       <c r="E49" t="n">
-        <v>978</v>
+        <v>940</v>
       </c>
       <c r="F49" t="n">
-        <v>951</v>
+        <v>892</v>
       </c>
       <c r="G49" t="n">
-        <v>945</v>
+        <v>1008</v>
       </c>
       <c r="H49" t="n">
-        <v>837</v>
+        <v>972</v>
       </c>
       <c r="I49" t="n">
-        <v>933</v>
+        <v>921</v>
       </c>
       <c r="J49" t="n">
-        <v>800</v>
+        <v>892</v>
       </c>
       <c r="K49" t="n">
-        <v>915</v>
+        <v>998</v>
       </c>
       <c r="L49" t="n">
-        <v>912.7</v>
+        <v>938.5</v>
       </c>
     </row>
     <row r="50">
@@ -2295,37 +2295,37 @@
         <v>8</v>
       </c>
       <c r="B50" t="n">
-        <v>893</v>
+        <v>847</v>
       </c>
       <c r="C50" t="n">
+        <v>860</v>
+      </c>
+      <c r="D50" t="n">
+        <v>986</v>
+      </c>
+      <c r="E50" t="n">
+        <v>864</v>
+      </c>
+      <c r="F50" t="n">
+        <v>955</v>
+      </c>
+      <c r="G50" t="n">
+        <v>1053</v>
+      </c>
+      <c r="H50" t="n">
+        <v>1055</v>
+      </c>
+      <c r="I50" t="n">
         <v>944</v>
       </c>
-      <c r="D50" t="n">
-        <v>963</v>
-      </c>
-      <c r="E50" t="n">
-        <v>722</v>
-      </c>
-      <c r="F50" t="n">
-        <v>1045</v>
-      </c>
-      <c r="G50" t="n">
-        <v>839</v>
-      </c>
-      <c r="H50" t="n">
-        <v>1006</v>
-      </c>
-      <c r="I50" t="n">
-        <v>987</v>
-      </c>
       <c r="J50" t="n">
-        <v>943</v>
+        <v>904</v>
       </c>
       <c r="K50" t="n">
-        <v>861</v>
+        <v>1012</v>
       </c>
       <c r="L50" t="n">
-        <v>920.3</v>
+        <v>948</v>
       </c>
     </row>
     <row r="51">
@@ -2333,37 +2333,37 @@
         <v>9</v>
       </c>
       <c r="B51" t="n">
-        <v>978</v>
+        <v>972</v>
       </c>
       <c r="C51" t="n">
-        <v>906</v>
+        <v>755</v>
       </c>
       <c r="D51" t="n">
-        <v>815</v>
+        <v>1009</v>
       </c>
       <c r="E51" t="n">
-        <v>871</v>
+        <v>983</v>
       </c>
       <c r="F51" t="n">
-        <v>956</v>
+        <v>912</v>
       </c>
       <c r="G51" t="n">
-        <v>822</v>
+        <v>992</v>
       </c>
       <c r="H51" t="n">
-        <v>871</v>
+        <v>922</v>
       </c>
       <c r="I51" t="n">
-        <v>934</v>
+        <v>882</v>
       </c>
       <c r="J51" t="n">
-        <v>871</v>
+        <v>941</v>
       </c>
       <c r="K51" t="n">
-        <v>864</v>
+        <v>866</v>
       </c>
       <c r="L51" t="n">
-        <v>888.8</v>
+        <v>923.4</v>
       </c>
     </row>
     <row r="52">
@@ -2373,37 +2373,37 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>878.36</v>
+        <v>919.8</v>
       </c>
       <c r="C52" t="n">
-        <v>924.96</v>
+        <v>873.6799999999999</v>
       </c>
       <c r="D52" t="n">
-        <v>886.84</v>
+        <v>905.7</v>
       </c>
       <c r="E52" t="n">
-        <v>905.14</v>
+        <v>909.02</v>
       </c>
       <c r="F52" t="n">
-        <v>905.52</v>
+        <v>901.46</v>
       </c>
       <c r="G52" t="n">
-        <v>898.74</v>
+        <v>919.5</v>
       </c>
       <c r="H52" t="n">
-        <v>898.28</v>
+        <v>901.16</v>
       </c>
       <c r="I52" t="n">
-        <v>922.7</v>
+        <v>905.88</v>
       </c>
       <c r="J52" t="n">
-        <v>883.28</v>
+        <v>912.96</v>
       </c>
       <c r="K52" t="n">
-        <v>905.6</v>
+        <v>922.26</v>
       </c>
       <c r="L52" t="n">
-        <v>900.9420000000001</v>
+        <v>907.1420000000002</v>
       </c>
     </row>
   </sheetData>
@@ -2462,37 +2462,37 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>7.45905613899231</v>
+        <v>7.86503529548645</v>
       </c>
       <c r="C2" t="n">
-        <v>6.378779888153076</v>
+        <v>6.352293014526367</v>
       </c>
       <c r="D2" t="n">
-        <v>6.236145257949829</v>
+        <v>8.160715818405151</v>
       </c>
       <c r="E2" t="n">
-        <v>9.388586044311523</v>
+        <v>7.531351089477539</v>
       </c>
       <c r="F2" t="n">
-        <v>7.494427919387817</v>
+        <v>6.292547464370728</v>
       </c>
       <c r="G2" t="n">
-        <v>6.715399742126465</v>
+        <v>6.870007038116455</v>
       </c>
       <c r="H2" t="n">
-        <v>6.356834888458252</v>
+        <v>6.446163892745972</v>
       </c>
       <c r="I2" t="n">
-        <v>8.229055166244507</v>
+        <v>9.303805351257324</v>
       </c>
       <c r="J2" t="n">
-        <v>7.037091732025146</v>
+        <v>7.088992118835449</v>
       </c>
       <c r="K2" t="n">
-        <v>7.013158798217773</v>
+        <v>8.497840642929077</v>
       </c>
       <c r="L2" t="n">
-        <v>7.23085355758667</v>
+        <v>7.440875172615051</v>
       </c>
     </row>
     <row r="3">
@@ -2500,37 +2500,37 @@
         <v>10</v>
       </c>
       <c r="B3" t="n">
-        <v>6.620141506195068</v>
+        <v>7.191031932830811</v>
       </c>
       <c r="C3" t="n">
-        <v>8.004623174667358</v>
+        <v>6.75593113899231</v>
       </c>
       <c r="D3" t="n">
-        <v>7.666482210159302</v>
+        <v>8.689916610717773</v>
       </c>
       <c r="E3" t="n">
-        <v>7.977684497833252</v>
+        <v>8.000242948532104</v>
       </c>
       <c r="F3" t="n">
-        <v>6.357322454452515</v>
+        <v>6.458192110061646</v>
       </c>
       <c r="G3" t="n">
-        <v>8.839021921157837</v>
+        <v>8.34330153465271</v>
       </c>
       <c r="H3" t="n">
-        <v>6.607672452926636</v>
+        <v>7.208270311355591</v>
       </c>
       <c r="I3" t="n">
-        <v>8.635504961013794</v>
+        <v>7.274095058441162</v>
       </c>
       <c r="J3" t="n">
-        <v>8.53776478767395</v>
+        <v>8.525360107421875</v>
       </c>
       <c r="K3" t="n">
-        <v>7.952224731445312</v>
+        <v>8.707942008972168</v>
       </c>
       <c r="L3" t="n">
-        <v>7.719844269752502</v>
+        <v>7.715428376197815</v>
       </c>
     </row>
     <row r="4">
@@ -2538,37 +2538,37 @@
         <v>11</v>
       </c>
       <c r="B4" t="n">
-        <v>6.243111848831177</v>
+        <v>9.862594127655029</v>
       </c>
       <c r="C4" t="n">
-        <v>6.380777835845947</v>
+        <v>6.914870262145996</v>
       </c>
       <c r="D4" t="n">
-        <v>6.352821826934814</v>
+        <v>9.139272928237915</v>
       </c>
       <c r="E4" t="n">
-        <v>6.350328207015991</v>
+        <v>6.468033313751221</v>
       </c>
       <c r="F4" t="n">
-        <v>6.222359657287598</v>
+        <v>6.243120431900024</v>
       </c>
       <c r="G4" t="n">
-        <v>5.989751815795898</v>
+        <v>7.511354923248291</v>
       </c>
       <c r="H4" t="n">
-        <v>6.280007839202881</v>
+        <v>6.021646022796631</v>
       </c>
       <c r="I4" t="n">
-        <v>6.474030733108521</v>
+        <v>6.843594789505005</v>
       </c>
       <c r="J4" t="n">
-        <v>6.362292289733887</v>
+        <v>8.989171266555786</v>
       </c>
       <c r="K4" t="n">
-        <v>6.005686283111572</v>
+        <v>6.698467969894409</v>
       </c>
       <c r="L4" t="n">
-        <v>6.266116833686828</v>
+        <v>7.469212603569031</v>
       </c>
     </row>
     <row r="5">
@@ -2576,37 +2576,37 @@
         <v>12</v>
       </c>
       <c r="B5" t="n">
-        <v>6.564314126968384</v>
+        <v>8.114913940429688</v>
       </c>
       <c r="C5" t="n">
-        <v>7.124357223510742</v>
+        <v>6.511427640914917</v>
       </c>
       <c r="D5" t="n">
-        <v>6.454541206359863</v>
+        <v>6.222887516021729</v>
       </c>
       <c r="E5" t="n">
-        <v>6.651582717895508</v>
+        <v>6.011389255523682</v>
       </c>
       <c r="F5" t="n">
-        <v>6.148861408233643</v>
+        <v>6.67817497253418</v>
       </c>
       <c r="G5" t="n">
-        <v>7.292904853820801</v>
+        <v>8.519345283508301</v>
       </c>
       <c r="H5" t="n">
-        <v>5.904505729675293</v>
+        <v>8.857012987136841</v>
       </c>
       <c r="I5" t="n">
-        <v>7.269543409347534</v>
+        <v>7.69934344291687</v>
       </c>
       <c r="J5" t="n">
-        <v>5.534405946731567</v>
+        <v>5.938057899475098</v>
       </c>
       <c r="K5" t="n">
-        <v>6.013680219650269</v>
+        <v>6.244797945022583</v>
       </c>
       <c r="L5" t="n">
-        <v>6.49586968421936</v>
+        <v>7.079735088348388</v>
       </c>
     </row>
     <row r="6">
@@ -2614,37 +2614,37 @@
         <v>13</v>
       </c>
       <c r="B6" t="n">
-        <v>5.392779588699341</v>
+        <v>6.315099477767944</v>
       </c>
       <c r="C6" t="n">
-        <v>5.541897535324097</v>
+        <v>5.845828771591187</v>
       </c>
       <c r="D6" t="n">
-        <v>5.308979272842407</v>
+        <v>5.961021900177002</v>
       </c>
       <c r="E6" t="n">
-        <v>6.088542222976685</v>
+        <v>5.59957480430603</v>
       </c>
       <c r="F6" t="n">
-        <v>5.796277046203613</v>
+        <v>6.641790390014648</v>
       </c>
       <c r="G6" t="n">
-        <v>7.68194580078125</v>
+        <v>6.362500429153442</v>
       </c>
       <c r="H6" t="n">
-        <v>5.258597612380981</v>
+        <v>5.679804563522339</v>
       </c>
       <c r="I6" t="n">
-        <v>5.428186178207397</v>
+        <v>7.597716093063354</v>
       </c>
       <c r="J6" t="n">
-        <v>5.500505208969116</v>
+        <v>7.754864692687988</v>
       </c>
       <c r="K6" t="n">
-        <v>5.458611965179443</v>
+        <v>7.712480783462524</v>
       </c>
       <c r="L6" t="n">
-        <v>5.745632243156433</v>
+        <v>6.547068190574646</v>
       </c>
     </row>
     <row r="7">
@@ -2652,37 +2652,37 @@
         <v>14</v>
       </c>
       <c r="B7" t="n">
-        <v>8.127799510955811</v>
+        <v>7.564932823181152</v>
       </c>
       <c r="C7" t="n">
-        <v>8.778624773025513</v>
+        <v>8.147042036056519</v>
       </c>
       <c r="D7" t="n">
-        <v>6.407181262969971</v>
+        <v>7.199715375900269</v>
       </c>
       <c r="E7" t="n">
-        <v>8.895829439163208</v>
+        <v>7.584290027618408</v>
       </c>
       <c r="F7" t="n">
-        <v>7.709871530532837</v>
+        <v>7.426121234893799</v>
       </c>
       <c r="G7" t="n">
-        <v>6.906913280487061</v>
+        <v>10.49294137954712</v>
       </c>
       <c r="H7" t="n">
-        <v>6.96576189994812</v>
+        <v>7.564805507659912</v>
       </c>
       <c r="I7" t="n">
-        <v>8.961183786392212</v>
+        <v>7.133949279785156</v>
       </c>
       <c r="J7" t="n">
-        <v>7.16423773765564</v>
+        <v>7.7497878074646</v>
       </c>
       <c r="K7" t="n">
-        <v>7.236075639724731</v>
+        <v>7.290953397750854</v>
       </c>
       <c r="L7" t="n">
-        <v>7.71534788608551</v>
+        <v>7.815453886985779</v>
       </c>
     </row>
     <row r="8">
@@ -2690,37 +2690,37 @@
         <v>15</v>
       </c>
       <c r="B8" t="n">
-        <v>6.337433099746704</v>
+        <v>8.863410949707031</v>
       </c>
       <c r="C8" t="n">
-        <v>6.943844795227051</v>
+        <v>6.870076417922974</v>
       </c>
       <c r="D8" t="n">
-        <v>6.292484760284424</v>
+        <v>6.756355762481689</v>
       </c>
       <c r="E8" t="n">
-        <v>6.862498760223389</v>
+        <v>6.525893926620483</v>
       </c>
       <c r="F8" t="n">
-        <v>6.616167783737183</v>
+        <v>7.339352369308472</v>
       </c>
       <c r="G8" t="n">
-        <v>6.886988162994385</v>
+        <v>7.775712013244629</v>
       </c>
       <c r="H8" t="n">
-        <v>6.955779075622559</v>
+        <v>7.895405054092407</v>
       </c>
       <c r="I8" t="n">
-        <v>7.695925235748291</v>
+        <v>7.586681604385376</v>
       </c>
       <c r="J8" t="n">
-        <v>7.073493003845215</v>
+        <v>7.713254928588867</v>
       </c>
       <c r="K8" t="n">
-        <v>6.853559970855713</v>
+        <v>9.230995178222656</v>
       </c>
       <c r="L8" t="n">
-        <v>6.851817464828491</v>
+        <v>7.655713820457459</v>
       </c>
     </row>
     <row r="9">
@@ -2728,37 +2728,37 @@
         <v>16</v>
       </c>
       <c r="B9" t="n">
-        <v>9.14625096321106</v>
+        <v>8.87946081161499</v>
       </c>
       <c r="C9" t="n">
-        <v>9.006032228469849</v>
+        <v>7.212262153625488</v>
       </c>
       <c r="D9" t="n">
-        <v>6.451583862304688</v>
+        <v>7.433651447296143</v>
       </c>
       <c r="E9" t="n">
-        <v>8.093873262405396</v>
+        <v>6.775898456573486</v>
       </c>
       <c r="F9" t="n">
-        <v>6.561792135238647</v>
+        <v>7.043203353881836</v>
       </c>
       <c r="G9" t="n">
-        <v>9.438942193984985</v>
+        <v>6.981346845626831</v>
       </c>
       <c r="H9" t="n">
-        <v>9.233505010604858</v>
+        <v>8.052546977996826</v>
       </c>
       <c r="I9" t="n">
-        <v>6.615034341812134</v>
+        <v>6.911543846130371</v>
       </c>
       <c r="J9" t="n">
-        <v>8.741290092468262</v>
+        <v>6.566422462463379</v>
       </c>
       <c r="K9" t="n">
-        <v>6.730008125305176</v>
+        <v>7.919906139373779</v>
       </c>
       <c r="L9" t="n">
-        <v>8.001831221580506</v>
+        <v>7.377624249458313</v>
       </c>
     </row>
     <row r="10">
@@ -2766,37 +2766,37 @@
         <v>17</v>
       </c>
       <c r="B10" t="n">
-        <v>6.193402290344238</v>
+        <v>8.260504722595215</v>
       </c>
       <c r="C10" t="n">
-        <v>7.862506866455078</v>
+        <v>8.244598150253296</v>
       </c>
       <c r="D10" t="n">
-        <v>8.344241380691528</v>
+        <v>6.275863885879517</v>
       </c>
       <c r="E10" t="n">
-        <v>5.651610136032104</v>
+        <v>8.033524036407471</v>
       </c>
       <c r="F10" t="n">
-        <v>6.149349451065063</v>
+        <v>7.407562494277954</v>
       </c>
       <c r="G10" t="n">
-        <v>5.795245409011841</v>
+        <v>7.641568899154663</v>
       </c>
       <c r="H10" t="n">
-        <v>6.150830507278442</v>
+        <v>7.798140525817871</v>
       </c>
       <c r="I10" t="n">
-        <v>8.69239068031311</v>
+        <v>6.322397708892822</v>
       </c>
       <c r="J10" t="n">
-        <v>6.033624172210693</v>
+        <v>6.28052544593811</v>
       </c>
       <c r="K10" t="n">
-        <v>8.157740116119385</v>
+        <v>7.919343709945679</v>
       </c>
       <c r="L10" t="n">
-        <v>6.903094100952148</v>
+        <v>7.41840295791626</v>
       </c>
     </row>
     <row r="11">
@@ -2804,37 +2804,37 @@
         <v>18</v>
       </c>
       <c r="B11" t="n">
-        <v>6.615167379379272</v>
+        <v>7.149287700653076</v>
       </c>
       <c r="C11" t="n">
-        <v>6.561275243759155</v>
+        <v>6.299461603164673</v>
       </c>
       <c r="D11" t="n">
-        <v>6.130913019180298</v>
+        <v>7.285987138748169</v>
       </c>
       <c r="E11" t="n">
-        <v>6.743354320526123</v>
+        <v>7.166266918182373</v>
       </c>
       <c r="F11" t="n">
-        <v>6.420758247375488</v>
+        <v>7.011160135269165</v>
       </c>
       <c r="G11" t="n">
-        <v>8.06596827507019</v>
+        <v>6.516863822937012</v>
       </c>
       <c r="H11" t="n">
-        <v>6.353314399719238</v>
+        <v>7.760096549987793</v>
       </c>
       <c r="I11" t="n">
-        <v>6.592212438583374</v>
+        <v>6.664158344268799</v>
       </c>
       <c r="J11" t="n">
-        <v>6.830653190612793</v>
+        <v>6.622786283493042</v>
       </c>
       <c r="K11" t="n">
-        <v>6.566790580749512</v>
+        <v>8.988619089126587</v>
       </c>
       <c r="L11" t="n">
-        <v>6.688040709495544</v>
+        <v>7.146468758583069</v>
       </c>
     </row>
     <row r="12">
@@ -2842,37 +2842,37 @@
         <v>19</v>
       </c>
       <c r="B12" t="n">
-        <v>8.932753324508667</v>
+        <v>8.556268453598022</v>
       </c>
       <c r="C12" t="n">
-        <v>6.741331338882446</v>
+        <v>8.044084310531616</v>
       </c>
       <c r="D12" t="n">
-        <v>7.657532930374146</v>
+        <v>6.985820293426514</v>
       </c>
       <c r="E12" t="n">
-        <v>8.440990924835205</v>
+        <v>7.941849946975708</v>
       </c>
       <c r="F12" t="n">
-        <v>7.196173906326294</v>
+        <v>8.446540594100952</v>
       </c>
       <c r="G12" t="n">
-        <v>8.415584564208984</v>
+        <v>6.670669794082642</v>
       </c>
       <c r="H12" t="n">
-        <v>6.71744704246521</v>
+        <v>7.326471328735352</v>
       </c>
       <c r="I12" t="n">
-        <v>7.512950420379639</v>
+        <v>9.010578155517578</v>
       </c>
       <c r="J12" t="n">
-        <v>7.828655958175659</v>
+        <v>9.800489187240601</v>
       </c>
       <c r="K12" t="n">
-        <v>7.920894145965576</v>
+        <v>9.907743453979492</v>
       </c>
       <c r="L12" t="n">
-        <v>7.736431455612182</v>
+        <v>8.269051551818848</v>
       </c>
     </row>
     <row r="13">
@@ -2880,37 +2880,37 @@
         <v>2</v>
       </c>
       <c r="B13" t="n">
-        <v>7.583588361740112</v>
+        <v>5.84880518913269</v>
       </c>
       <c r="C13" t="n">
-        <v>7.528330326080322</v>
+        <v>6.341553211212158</v>
       </c>
       <c r="D13" t="n">
-        <v>8.065958023071289</v>
+        <v>6.730003833770752</v>
       </c>
       <c r="E13" t="n">
-        <v>5.848127126693726</v>
+        <v>7.806708812713623</v>
       </c>
       <c r="F13" t="n">
-        <v>5.993733644485474</v>
+        <v>6.858167171478271</v>
       </c>
       <c r="G13" t="n">
-        <v>6.987237215042114</v>
+        <v>6.910516262054443</v>
       </c>
       <c r="H13" t="n">
-        <v>6.05660343170166</v>
+        <v>7.503957748413086</v>
       </c>
       <c r="I13" t="n">
-        <v>5.497497797012329</v>
+        <v>7.084062337875366</v>
       </c>
       <c r="J13" t="n">
-        <v>5.633663892745972</v>
+        <v>6.169460773468018</v>
       </c>
       <c r="K13" t="n">
-        <v>6.107980489730835</v>
+        <v>5.812901020050049</v>
       </c>
       <c r="L13" t="n">
-        <v>6.530272030830384</v>
+        <v>6.706613636016845</v>
       </c>
     </row>
     <row r="14">
@@ -2918,37 +2918,37 @@
         <v>20</v>
       </c>
       <c r="B14" t="n">
-        <v>7.468502759933472</v>
+        <v>7.186289310455322</v>
       </c>
       <c r="C14" t="n">
-        <v>8.192639112472534</v>
+        <v>6.531512260437012</v>
       </c>
       <c r="D14" t="n">
-        <v>7.691934823989868</v>
+        <v>7.2371985912323</v>
       </c>
       <c r="E14" t="n">
-        <v>7.111408233642578</v>
+        <v>7.415710210800171</v>
       </c>
       <c r="F14" t="n">
-        <v>7.869130373001099</v>
+        <v>6.703071355819702</v>
       </c>
       <c r="G14" t="n">
-        <v>7.024115562438965</v>
+        <v>7.205272912979126</v>
       </c>
       <c r="H14" t="n">
-        <v>7.958230018615723</v>
+        <v>6.973902225494385</v>
       </c>
       <c r="I14" t="n">
-        <v>7.193701267242432</v>
+        <v>6.890083074569702</v>
       </c>
       <c r="J14" t="n">
-        <v>7.115380048751831</v>
+        <v>8.324841976165771</v>
       </c>
       <c r="K14" t="n">
-        <v>6.771254777908325</v>
+        <v>7.497538805007935</v>
       </c>
       <c r="L14" t="n">
-        <v>7.439629697799683</v>
+        <v>7.196542072296142</v>
       </c>
     </row>
     <row r="15">
@@ -2956,37 +2956,37 @@
         <v>21</v>
       </c>
       <c r="B15" t="n">
-        <v>6.20821213722229</v>
+        <v>6.869155168533325</v>
       </c>
       <c r="C15" t="n">
-        <v>8.276448726654053</v>
+        <v>6.176948547363281</v>
       </c>
       <c r="D15" t="n">
-        <v>7.31585693359375</v>
+        <v>10.55802178382874</v>
       </c>
       <c r="E15" t="n">
-        <v>6.394743919372559</v>
+        <v>7.326459169387817</v>
       </c>
       <c r="F15" t="n">
-        <v>6.649063348770142</v>
+        <v>6.431272983551025</v>
       </c>
       <c r="G15" t="n">
-        <v>8.856471300125122</v>
+        <v>6.854699611663818</v>
       </c>
       <c r="H15" t="n">
-        <v>6.440119028091431</v>
+        <v>6.476158857345581</v>
       </c>
       <c r="I15" t="n">
-        <v>6.40018105506897</v>
+        <v>6.582866668701172</v>
       </c>
       <c r="J15" t="n">
-        <v>6.59618616104126</v>
+        <v>6.569908142089844</v>
       </c>
       <c r="K15" t="n">
-        <v>9.683834075927734</v>
+        <v>8.338797092437744</v>
       </c>
       <c r="L15" t="n">
-        <v>7.282111668586731</v>
+        <v>7.218428802490235</v>
       </c>
     </row>
     <row r="16">
@@ -2994,37 +2994,37 @@
         <v>22</v>
       </c>
       <c r="B16" t="n">
-        <v>6.474014282226562</v>
+        <v>6.862662553787231</v>
       </c>
       <c r="C16" t="n">
-        <v>7.718817234039307</v>
+        <v>8.46098518371582</v>
       </c>
       <c r="D16" t="n">
-        <v>6.708455324172974</v>
+        <v>8.307908296585083</v>
       </c>
       <c r="E16" t="n">
-        <v>6.584717273712158</v>
+        <v>9.204071998596191</v>
       </c>
       <c r="F16" t="n">
-        <v>7.876439571380615</v>
+        <v>6.473188161849976</v>
       </c>
       <c r="G16" t="n">
-        <v>6.712396860122681</v>
+        <v>8.193207740783691</v>
       </c>
       <c r="H16" t="n">
-        <v>6.848579168319702</v>
+        <v>7.305969715118408</v>
       </c>
       <c r="I16" t="n">
-        <v>6.469034910202026</v>
+        <v>6.372771739959717</v>
       </c>
       <c r="J16" t="n">
-        <v>6.490474462509155</v>
+        <v>6.499423027038574</v>
       </c>
       <c r="K16" t="n">
-        <v>9.672873258590698</v>
+        <v>7.508373022079468</v>
       </c>
       <c r="L16" t="n">
-        <v>7.155580234527588</v>
+        <v>7.518856143951416</v>
       </c>
     </row>
     <row r="17">
@@ -3032,37 +3032,37 @@
         <v>23</v>
       </c>
       <c r="B17" t="n">
-        <v>7.770713090896606</v>
+        <v>7.080960750579834</v>
       </c>
       <c r="C17" t="n">
-        <v>8.023068428039551</v>
+        <v>7.347319364547729</v>
       </c>
       <c r="D17" t="n">
-        <v>8.537772655487061</v>
+        <v>6.789221048355103</v>
       </c>
       <c r="E17" t="n">
-        <v>7.117371082305908</v>
+        <v>9.361183643341064</v>
       </c>
       <c r="F17" t="n">
-        <v>7.021158933639526</v>
+        <v>8.885375261306763</v>
       </c>
       <c r="G17" t="n">
-        <v>10.15263032913208</v>
+        <v>7.340300798416138</v>
       </c>
       <c r="H17" t="n">
-        <v>9.497287511825562</v>
+        <v>7.642555475234985</v>
       </c>
       <c r="I17" t="n">
-        <v>8.486385345458984</v>
+        <v>8.20911979675293</v>
       </c>
       <c r="J17" t="n">
-        <v>10.78057646751404</v>
+        <v>7.578195333480835</v>
       </c>
       <c r="K17" t="n">
-        <v>6.568048000335693</v>
+        <v>6.66253137588501</v>
       </c>
       <c r="L17" t="n">
-        <v>8.395501184463502</v>
+        <v>7.689676284790039</v>
       </c>
     </row>
     <row r="18">
@@ -3070,37 +3070,37 @@
         <v>24</v>
       </c>
       <c r="B18" t="n">
-        <v>6.597187995910645</v>
+        <v>6.365270376205444</v>
       </c>
       <c r="C18" t="n">
-        <v>5.781776189804077</v>
+        <v>7.750747442245483</v>
       </c>
       <c r="D18" t="n">
-        <v>6.163726329803467</v>
+        <v>10.08685302734375</v>
       </c>
       <c r="E18" t="n">
-        <v>7.302520275115967</v>
+        <v>6.251859903335571</v>
       </c>
       <c r="F18" t="n">
-        <v>7.051070213317871</v>
+        <v>6.43111515045166</v>
       </c>
       <c r="G18" t="n">
-        <v>6.530895233154297</v>
+        <v>9.330736875534058</v>
       </c>
       <c r="H18" t="n">
-        <v>7.141293525695801</v>
+        <v>6.679989337921143</v>
       </c>
       <c r="I18" t="n">
-        <v>6.070088148117065</v>
+        <v>9.040330648422241</v>
       </c>
       <c r="J18" t="n">
-        <v>6.120902538299561</v>
+        <v>6.116917848587036</v>
       </c>
       <c r="K18" t="n">
-        <v>6.271035432815552</v>
+        <v>6.819633722305298</v>
       </c>
       <c r="L18" t="n">
-        <v>6.50304958820343</v>
+        <v>7.487345433235168</v>
       </c>
     </row>
     <row r="19">
@@ -3108,37 +3108,37 @@
         <v>25</v>
       </c>
       <c r="B19" t="n">
-        <v>7.161277294158936</v>
+        <v>6.351365089416504</v>
       </c>
       <c r="C19" t="n">
-        <v>7.190699100494385</v>
+        <v>5.814186573028564</v>
       </c>
       <c r="D19" t="n">
-        <v>5.875011444091797</v>
+        <v>6.046626329421997</v>
       </c>
       <c r="E19" t="n">
-        <v>6.201224803924561</v>
+        <v>6.229658842086792</v>
       </c>
       <c r="F19" t="n">
-        <v>6.139367341995239</v>
+        <v>8.455460548400879</v>
       </c>
       <c r="G19" t="n">
-        <v>6.68594765663147</v>
+        <v>7.704851627349854</v>
       </c>
       <c r="H19" t="n">
-        <v>6.092015504837036</v>
+        <v>7.453002691268921</v>
       </c>
       <c r="I19" t="n">
-        <v>7.43109917640686</v>
+        <v>7.619578838348389</v>
       </c>
       <c r="J19" t="n">
-        <v>6.956332445144653</v>
+        <v>7.505373001098633</v>
       </c>
       <c r="K19" t="n">
-        <v>6.660051584243774</v>
+        <v>7.644561052322388</v>
       </c>
       <c r="L19" t="n">
-        <v>6.639302635192871</v>
+        <v>7.082466459274292</v>
       </c>
     </row>
     <row r="20">
@@ -3146,37 +3146,37 @@
         <v>26</v>
       </c>
       <c r="B20" t="n">
-        <v>7.348302125930786</v>
+        <v>8.791601419448853</v>
       </c>
       <c r="C20" t="n">
-        <v>9.109821557998657</v>
+        <v>8.198606729507446</v>
       </c>
       <c r="D20" t="n">
-        <v>7.081483364105225</v>
+        <v>7.335313558578491</v>
       </c>
       <c r="E20" t="n">
-        <v>9.497298002243042</v>
+        <v>6.506927728652954</v>
       </c>
       <c r="F20" t="n">
-        <v>9.172123193740845</v>
+        <v>6.639113664627075</v>
       </c>
       <c r="G20" t="n">
-        <v>7.298918485641479</v>
+        <v>8.000609159469604</v>
       </c>
       <c r="H20" t="n">
-        <v>6.737392425537109</v>
+        <v>6.750308275222778</v>
       </c>
       <c r="I20" t="n">
-        <v>6.988234043121338</v>
+        <v>9.322757720947266</v>
       </c>
       <c r="J20" t="n">
-        <v>6.584323644638062</v>
+        <v>8.770129203796387</v>
       </c>
       <c r="K20" t="n">
-        <v>8.696370124816895</v>
+        <v>6.382720232009888</v>
       </c>
       <c r="L20" t="n">
-        <v>7.851426696777343</v>
+        <v>7.669808769226075</v>
       </c>
     </row>
     <row r="21">
@@ -3184,37 +3184,37 @@
         <v>27</v>
       </c>
       <c r="B21" t="n">
-        <v>7.460602045059204</v>
+        <v>8.363718509674072</v>
       </c>
       <c r="C21" t="n">
-        <v>8.226049661636353</v>
+        <v>8.209092855453491</v>
       </c>
       <c r="D21" t="n">
-        <v>7.776723384857178</v>
+        <v>6.813661098480225</v>
       </c>
       <c r="E21" t="n">
-        <v>7.810119867324829</v>
+        <v>6.479487895965576</v>
       </c>
       <c r="F21" t="n">
-        <v>6.775776624679565</v>
+        <v>7.312913417816162</v>
       </c>
       <c r="G21" t="n">
-        <v>9.723741292953491</v>
+        <v>7.86950159072876</v>
       </c>
       <c r="H21" t="n">
-        <v>7.033097505569458</v>
+        <v>7.480936765670776</v>
       </c>
       <c r="I21" t="n">
-        <v>8.506884813308716</v>
+        <v>8.139286994934082</v>
       </c>
       <c r="J21" t="n">
-        <v>8.240010738372803</v>
+        <v>7.947259664535522</v>
       </c>
       <c r="K21" t="n">
-        <v>7.455030202865601</v>
+        <v>7.866994142532349</v>
       </c>
       <c r="L21" t="n">
-        <v>7.90080361366272</v>
+        <v>7.648285293579102</v>
       </c>
     </row>
     <row r="22">
@@ -3222,37 +3222,37 @@
         <v>28</v>
       </c>
       <c r="B22" t="n">
-        <v>6.195228815078735</v>
+        <v>7.212093114852905</v>
       </c>
       <c r="C22" t="n">
-        <v>5.894490480422974</v>
+        <v>5.594747304916382</v>
       </c>
       <c r="D22" t="n">
-        <v>6.047634124755859</v>
+        <v>6.716430902481079</v>
       </c>
       <c r="E22" t="n">
-        <v>5.888505697250366</v>
+        <v>5.803214550018311</v>
       </c>
       <c r="F22" t="n">
-        <v>6.220146894454956</v>
+        <v>6.211178541183472</v>
       </c>
       <c r="G22" t="n">
-        <v>6.77276086807251</v>
+        <v>5.8062584400177</v>
       </c>
       <c r="H22" t="n">
-        <v>6.424617290496826</v>
+        <v>5.841134548187256</v>
       </c>
       <c r="I22" t="n">
-        <v>7.622595310211182</v>
+        <v>7.403136968612671</v>
       </c>
       <c r="J22" t="n">
-        <v>6.301450490951538</v>
+        <v>6.119909763336182</v>
       </c>
       <c r="K22" t="n">
-        <v>6.25209641456604</v>
+        <v>5.669077157974243</v>
       </c>
       <c r="L22" t="n">
-        <v>6.361952638626098</v>
+        <v>6.23771812915802</v>
       </c>
     </row>
     <row r="23">
@@ -3260,37 +3260,37 @@
         <v>29</v>
       </c>
       <c r="B23" t="n">
-        <v>8.194141864776611</v>
+        <v>7.69095253944397</v>
       </c>
       <c r="C23" t="n">
-        <v>8.395633935928345</v>
+        <v>10.01450061798096</v>
       </c>
       <c r="D23" t="n">
-        <v>9.425993919372559</v>
+        <v>9.055927515029907</v>
       </c>
       <c r="E23" t="n">
-        <v>7.255574464797974</v>
+        <v>7.424096345901489</v>
       </c>
       <c r="F23" t="n">
-        <v>7.665957927703857</v>
+        <v>8.14773154258728</v>
       </c>
       <c r="G23" t="n">
-        <v>10.84534454345703</v>
+        <v>10.18482041358948</v>
       </c>
       <c r="H23" t="n">
-        <v>8.536782264709473</v>
+        <v>9.107827186584473</v>
       </c>
       <c r="I23" t="n">
-        <v>9.579642534255981</v>
+        <v>7.759315252304077</v>
       </c>
       <c r="J23" t="n">
-        <v>8.516870975494385</v>
+        <v>9.389581441879272</v>
       </c>
       <c r="K23" t="n">
-        <v>7.978152751922607</v>
+        <v>8.620558977127075</v>
       </c>
       <c r="L23" t="n">
-        <v>8.639409518241882</v>
+        <v>8.739531183242798</v>
       </c>
     </row>
     <row r="24">
@@ -3298,37 +3298,37 @@
         <v>3</v>
       </c>
       <c r="B24" t="n">
-        <v>6.93984055519104</v>
+        <v>9.504886388778687</v>
       </c>
       <c r="C24" t="n">
-        <v>6.733813524246216</v>
+        <v>10.59442138671875</v>
       </c>
       <c r="D24" t="n">
-        <v>7.069990634918213</v>
+        <v>7.206248998641968</v>
       </c>
       <c r="E24" t="n">
-        <v>8.367715120315552</v>
+        <v>8.856955766677856</v>
       </c>
       <c r="F24" t="n">
-        <v>9.395544052124023</v>
+        <v>8.648483276367188</v>
       </c>
       <c r="G24" t="n">
-        <v>10.70922780036926</v>
+        <v>7.883012294769287</v>
       </c>
       <c r="H24" t="n">
-        <v>6.698455095291138</v>
+        <v>10.64930415153503</v>
       </c>
       <c r="I24" t="n">
-        <v>8.579561233520508</v>
+        <v>7.104012012481689</v>
       </c>
       <c r="J24" t="n">
-        <v>9.518008232116699</v>
+        <v>9.534674167633057</v>
       </c>
       <c r="K24" t="n">
-        <v>9.41899299621582</v>
+        <v>7.001879692077637</v>
       </c>
       <c r="L24" t="n">
-        <v>8.343114924430846</v>
+        <v>8.698387813568115</v>
       </c>
     </row>
     <row r="25">
@@ -3336,37 +3336,37 @@
         <v>30</v>
       </c>
       <c r="B25" t="n">
-        <v>6.397196769714355</v>
+        <v>7.080092191696167</v>
       </c>
       <c r="C25" t="n">
-        <v>6.921473979949951</v>
+        <v>6.356966495513916</v>
       </c>
       <c r="D25" t="n">
-        <v>6.57776141166687</v>
+        <v>6.898574113845825</v>
       </c>
       <c r="E25" t="n">
-        <v>6.892966508865356</v>
+        <v>7.45262622833252</v>
       </c>
       <c r="F25" t="n">
-        <v>7.890451908111572</v>
+        <v>8.287904024124146</v>
       </c>
       <c r="G25" t="n">
-        <v>6.258056402206421</v>
+        <v>6.886608362197876</v>
       </c>
       <c r="H25" t="n">
-        <v>6.340403079986572</v>
+        <v>6.613807439804077</v>
       </c>
       <c r="I25" t="n">
-        <v>7.000175952911377</v>
+        <v>8.160265684127808</v>
       </c>
       <c r="J25" t="n">
-        <v>6.418683528900146</v>
+        <v>9.512779235839844</v>
       </c>
       <c r="K25" t="n">
-        <v>6.707091808319092</v>
+        <v>6.419393539428711</v>
       </c>
       <c r="L25" t="n">
-        <v>6.740426135063172</v>
+        <v>7.366901731491089</v>
       </c>
     </row>
     <row r="26">
@@ -3374,37 +3374,37 @@
         <v>31</v>
       </c>
       <c r="B26" t="n">
-        <v>6.321460008621216</v>
+        <v>6.422643184661865</v>
       </c>
       <c r="C26" t="n">
-        <v>7.858764886856079</v>
+        <v>6.923415899276733</v>
       </c>
       <c r="D26" t="n">
-        <v>6.676629304885864</v>
+        <v>6.410541772842407</v>
       </c>
       <c r="E26" t="n">
-        <v>6.381412029266357</v>
+        <v>8.558238983154297</v>
       </c>
       <c r="F26" t="n">
-        <v>6.175941228866577</v>
+        <v>8.75869345664978</v>
       </c>
       <c r="G26" t="n">
-        <v>9.658736944198608</v>
+        <v>6.765401601791382</v>
       </c>
       <c r="H26" t="n">
-        <v>6.575397729873657</v>
+        <v>7.832646608352661</v>
       </c>
       <c r="I26" t="n">
-        <v>8.715819358825684</v>
+        <v>6.794299602508545</v>
       </c>
       <c r="J26" t="n">
-        <v>6.967887878417969</v>
+        <v>6.285645484924316</v>
       </c>
       <c r="K26" t="n">
-        <v>9.347202777862549</v>
+        <v>8.806215286254883</v>
       </c>
       <c r="L26" t="n">
-        <v>7.467925214767456</v>
+        <v>7.355774188041687</v>
       </c>
     </row>
     <row r="27">
@@ -3412,37 +3412,37 @@
         <v>32</v>
       </c>
       <c r="B27" t="n">
-        <v>9.242972612380981</v>
+        <v>10.01793265342712</v>
       </c>
       <c r="C27" t="n">
-        <v>8.453529596328735</v>
+        <v>9.362160921096802</v>
       </c>
       <c r="D27" t="n">
-        <v>6.312489748001099</v>
+        <v>9.598026514053345</v>
       </c>
       <c r="E27" t="n">
-        <v>9.590098857879639</v>
+        <v>8.974652528762817</v>
       </c>
       <c r="F27" t="n">
-        <v>8.937729358673096</v>
+        <v>7.912915945053101</v>
       </c>
       <c r="G27" t="n">
-        <v>9.632997274398804</v>
+        <v>7.068604230880737</v>
       </c>
       <c r="H27" t="n">
-        <v>9.442968845367432</v>
+        <v>6.908562183380127</v>
       </c>
       <c r="I27" t="n">
-        <v>7.361748456954956</v>
+        <v>10.3136682510376</v>
       </c>
       <c r="J27" t="n">
-        <v>6.720386743545532</v>
+        <v>8.749778032302856</v>
       </c>
       <c r="K27" t="n">
-        <v>7.380231380462646</v>
+        <v>7.847365617752075</v>
       </c>
       <c r="L27" t="n">
-        <v>8.307515287399292</v>
+        <v>8.675366687774659</v>
       </c>
     </row>
     <row r="28">
@@ -3450,37 +3450,37 @@
         <v>33</v>
       </c>
       <c r="B28" t="n">
-        <v>7.026082754135132</v>
+        <v>8.106840848922729</v>
       </c>
       <c r="C28" t="n">
-        <v>6.913918256759644</v>
+        <v>8.14281964302063</v>
       </c>
       <c r="D28" t="n">
-        <v>7.46100378036499</v>
+        <v>12.56179881095886</v>
       </c>
       <c r="E28" t="n">
-        <v>7.281986474990845</v>
+        <v>9.089538335800171</v>
       </c>
       <c r="F28" t="n">
-        <v>7.30397629737854</v>
+        <v>8.407600164413452</v>
       </c>
       <c r="G28" t="n">
-        <v>8.407607793807983</v>
+        <v>7.038049697875977</v>
       </c>
       <c r="H28" t="n">
-        <v>7.223597526550293</v>
+        <v>9.131309509277344</v>
       </c>
       <c r="I28" t="n">
-        <v>7.887423276901245</v>
+        <v>8.223046779632568</v>
       </c>
       <c r="J28" t="n">
-        <v>7.366733312606812</v>
+        <v>7.05951714515686</v>
       </c>
       <c r="K28" t="n">
-        <v>7.691900730133057</v>
+        <v>7.061012029647827</v>
       </c>
       <c r="L28" t="n">
-        <v>7.456423020362854</v>
+        <v>8.482153296470642</v>
       </c>
     </row>
     <row r="29">
@@ -3488,37 +3488,37 @@
         <v>34</v>
       </c>
       <c r="B29" t="n">
-        <v>6.971750259399414</v>
+        <v>6.867025375366211</v>
       </c>
       <c r="C29" t="n">
-        <v>6.98523736000061</v>
+        <v>6.916874170303345</v>
       </c>
       <c r="D29" t="n">
-        <v>8.081905126571655</v>
+        <v>8.772157907485962</v>
       </c>
       <c r="E29" t="n">
-        <v>8.52077841758728</v>
+        <v>8.040504932403564</v>
       </c>
       <c r="F29" t="n">
-        <v>6.700436115264893</v>
+        <v>8.227059364318848</v>
       </c>
       <c r="G29" t="n">
-        <v>6.874486446380615</v>
+        <v>8.482398271560669</v>
       </c>
       <c r="H29" t="n">
-        <v>7.992655992507935</v>
+        <v>9.781126976013184</v>
       </c>
       <c r="I29" t="n">
-        <v>9.131232023239136</v>
+        <v>8.332313537597656</v>
       </c>
       <c r="J29" t="n">
-        <v>8.629095077514648</v>
+        <v>8.766103029251099</v>
       </c>
       <c r="K29" t="n">
-        <v>6.702438116073608</v>
+        <v>10.19006276130676</v>
       </c>
       <c r="L29" t="n">
-        <v>7.65900149345398</v>
+        <v>8.437562632560731</v>
       </c>
     </row>
     <row r="30">
@@ -3526,37 +3526,37 @@
         <v>35</v>
       </c>
       <c r="B30" t="n">
-        <v>7.644547700881958</v>
+        <v>8.054990768432617</v>
       </c>
       <c r="C30" t="n">
-        <v>8.203112125396729</v>
+        <v>7.970216512680054</v>
       </c>
       <c r="D30" t="n">
-        <v>7.109409332275391</v>
+        <v>7.732836961746216</v>
       </c>
       <c r="E30" t="n">
-        <v>9.152186155319214</v>
+        <v>7.015120267868042</v>
       </c>
       <c r="F30" t="n">
-        <v>8.817539691925049</v>
+        <v>8.126792430877686</v>
       </c>
       <c r="G30" t="n">
-        <v>8.599691152572632</v>
+        <v>10.71124887466431</v>
       </c>
       <c r="H30" t="n">
-        <v>9.003080129623413</v>
+        <v>8.491876125335693</v>
       </c>
       <c r="I30" t="n">
-        <v>8.19565224647522</v>
+        <v>8.835490703582764</v>
       </c>
       <c r="J30" t="n">
-        <v>6.603219032287598</v>
+        <v>9.9866042137146</v>
       </c>
       <c r="K30" t="n">
-        <v>9.608585357666016</v>
+        <v>9.072881460189819</v>
       </c>
       <c r="L30" t="n">
-        <v>8.293702292442322</v>
+        <v>8.59980583190918</v>
       </c>
     </row>
     <row r="31">
@@ -3564,37 +3564,37 @@
         <v>36</v>
       </c>
       <c r="B31" t="n">
-        <v>8.474945306777954</v>
+        <v>6.398703575134277</v>
       </c>
       <c r="C31" t="n">
-        <v>6.137867212295532</v>
+        <v>7.248583078384399</v>
       </c>
       <c r="D31" t="n">
-        <v>6.866032361984253</v>
+        <v>6.67851996421814</v>
       </c>
       <c r="E31" t="n">
-        <v>7.631573677062988</v>
+        <v>9.42896580696106</v>
       </c>
       <c r="F31" t="n">
-        <v>7.93428111076355</v>
+        <v>8.773680210113525</v>
       </c>
       <c r="G31" t="n">
-        <v>6.519894123077393</v>
+        <v>8.926755428314209</v>
       </c>
       <c r="H31" t="n">
-        <v>8.565709590911865</v>
+        <v>9.009038925170898</v>
       </c>
       <c r="I31" t="n">
-        <v>8.206081628799438</v>
+        <v>6.75627875328064</v>
       </c>
       <c r="J31" t="n">
-        <v>7.043060064315796</v>
+        <v>9.201543807983398</v>
       </c>
       <c r="K31" t="n">
-        <v>6.310415029525757</v>
+        <v>7.273464918136597</v>
       </c>
       <c r="L31" t="n">
-        <v>7.368986010551453</v>
+        <v>7.969553446769714</v>
       </c>
     </row>
     <row r="32">
@@ -3602,37 +3602,37 @@
         <v>37</v>
       </c>
       <c r="B32" t="n">
-        <v>8.337776899337769</v>
+        <v>8.22704029083252</v>
       </c>
       <c r="C32" t="n">
-        <v>8.224055290222168</v>
+        <v>6.413674354553223</v>
       </c>
       <c r="D32" t="n">
-        <v>7.151335954666138</v>
+        <v>8.128858327865601</v>
       </c>
       <c r="E32" t="n">
-        <v>6.08203125</v>
+        <v>7.081982135772705</v>
       </c>
       <c r="F32" t="n">
-        <v>7.571196556091309</v>
+        <v>7.793137550354004</v>
       </c>
       <c r="G32" t="n">
-        <v>6.341910600662231</v>
+        <v>6.257569074630737</v>
       </c>
       <c r="H32" t="n">
-        <v>8.894363403320312</v>
+        <v>7.710315942764282</v>
       </c>
       <c r="I32" t="n">
-        <v>6.829616546630859</v>
+        <v>8.05900764465332</v>
       </c>
       <c r="J32" t="n">
-        <v>6.213168621063232</v>
+        <v>6.053567171096802</v>
       </c>
       <c r="K32" t="n">
-        <v>6.250596761703491</v>
+        <v>6.745823860168457</v>
       </c>
       <c r="L32" t="n">
-        <v>7.189605188369751</v>
+        <v>7.247097635269165</v>
       </c>
     </row>
     <row r="33">
@@ -3640,37 +3640,37 @@
         <v>38</v>
       </c>
       <c r="B33" t="n">
-        <v>6.710469484329224</v>
+        <v>7.800131559371948</v>
       </c>
       <c r="C33" t="n">
-        <v>7.75572395324707</v>
+        <v>6.860167026519775</v>
       </c>
       <c r="D33" t="n">
-        <v>6.684496164321899</v>
+        <v>7.154265403747559</v>
       </c>
       <c r="E33" t="n">
-        <v>7.256551027297974</v>
+        <v>6.536340951919556</v>
       </c>
       <c r="F33" t="n">
-        <v>6.769758224487305</v>
+        <v>6.996661424636841</v>
       </c>
       <c r="G33" t="n">
-        <v>6.991216897964478</v>
+        <v>6.713515043258667</v>
       </c>
       <c r="H33" t="n">
-        <v>6.97272515296936</v>
+        <v>6.546942710876465</v>
       </c>
       <c r="I33" t="n">
-        <v>6.849083423614502</v>
+        <v>7.363801956176758</v>
       </c>
       <c r="J33" t="n">
-        <v>6.887463092803955</v>
+        <v>6.663518667221069</v>
       </c>
       <c r="K33" t="n">
-        <v>6.857631683349609</v>
+        <v>7.23057746887207</v>
       </c>
       <c r="L33" t="n">
-        <v>6.973511910438537</v>
+        <v>6.986592221260071</v>
       </c>
     </row>
     <row r="34">
@@ -3678,37 +3678,37 @@
         <v>39</v>
       </c>
       <c r="B34" t="n">
-        <v>8.767180442810059</v>
+        <v>6.068042755126953</v>
       </c>
       <c r="C34" t="n">
-        <v>8.3487548828125</v>
+        <v>6.66698169708252</v>
       </c>
       <c r="D34" t="n">
-        <v>8.235021352767944</v>
+        <v>5.81319522857666</v>
       </c>
       <c r="E34" t="n">
-        <v>7.045056343078613</v>
+        <v>5.912421464920044</v>
       </c>
       <c r="F34" t="n">
-        <v>7.249555587768555</v>
+        <v>8.307368040084839</v>
       </c>
       <c r="G34" t="n">
-        <v>7.462514877319336</v>
+        <v>6.322396516799927</v>
       </c>
       <c r="H34" t="n">
-        <v>8.381158828735352</v>
+        <v>6.798672199249268</v>
       </c>
       <c r="I34" t="n">
-        <v>7.973681211471558</v>
+        <v>7.772709608078003</v>
       </c>
       <c r="J34" t="n">
-        <v>6.84856390953064</v>
+        <v>5.842642545700073</v>
       </c>
       <c r="K34" t="n">
-        <v>5.712966203689575</v>
+        <v>6.041646957397461</v>
       </c>
       <c r="L34" t="n">
-        <v>7.602445363998413</v>
+        <v>6.554607701301575</v>
       </c>
     </row>
     <row r="35">
@@ -3716,37 +3716,37 @@
         <v>4</v>
       </c>
       <c r="B35" t="n">
-        <v>7.638063907623291</v>
+        <v>8.911810159683228</v>
       </c>
       <c r="C35" t="n">
-        <v>7.455088138580322</v>
+        <v>9.621460199356079</v>
       </c>
       <c r="D35" t="n">
-        <v>7.119398355484009</v>
+        <v>8.533894777297974</v>
       </c>
       <c r="E35" t="n">
-        <v>9.808001518249512</v>
+        <v>6.966901779174805</v>
       </c>
       <c r="F35" t="n">
-        <v>7.358785629272461</v>
+        <v>7.029693365097046</v>
       </c>
       <c r="G35" t="n">
-        <v>7.97567081451416</v>
+        <v>7.697505235671997</v>
       </c>
       <c r="H35" t="n">
-        <v>8.167725324630737</v>
+        <v>8.799725532531738</v>
       </c>
       <c r="I35" t="n">
-        <v>6.549339294433594</v>
+        <v>8.649005174636841</v>
       </c>
       <c r="J35" t="n">
-        <v>6.750292301177979</v>
+        <v>6.714054346084595</v>
       </c>
       <c r="K35" t="n">
-        <v>7.089461803436279</v>
+        <v>7.418705463409424</v>
       </c>
       <c r="L35" t="n">
-        <v>7.591182708740234</v>
+        <v>8.034275603294372</v>
       </c>
     </row>
     <row r="36">
@@ -3754,37 +3754,37 @@
         <v>40</v>
       </c>
       <c r="B36" t="n">
-        <v>9.102321147918701</v>
+        <v>11.00240921974182</v>
       </c>
       <c r="C36" t="n">
-        <v>9.326747179031372</v>
+        <v>7.253137350082397</v>
       </c>
       <c r="D36" t="n">
-        <v>7.506418943405151</v>
+        <v>7.235161066055298</v>
       </c>
       <c r="E36" t="n">
-        <v>7.816099166870117</v>
+        <v>8.911308288574219</v>
       </c>
       <c r="F36" t="n">
-        <v>10.17557406425476</v>
+        <v>10.74854040145874</v>
       </c>
       <c r="G36" t="n">
-        <v>8.3033447265625</v>
+        <v>9.143711090087891</v>
       </c>
       <c r="H36" t="n">
-        <v>9.175140619277954</v>
+        <v>7.92988920211792</v>
       </c>
       <c r="I36" t="n">
-        <v>8.87189507484436</v>
+        <v>7.438694953918457</v>
       </c>
       <c r="J36" t="n">
-        <v>10.07531642913818</v>
+        <v>9.077399492263794</v>
       </c>
       <c r="K36" t="n">
-        <v>10.1780858039856</v>
+        <v>8.555750131607056</v>
       </c>
       <c r="L36" t="n">
-        <v>9.05309431552887</v>
+        <v>8.72960011959076</v>
       </c>
     </row>
     <row r="37">
@@ -3792,37 +3792,37 @@
         <v>41</v>
       </c>
       <c r="B37" t="n">
-        <v>5.947368860244751</v>
+        <v>6.365929126739502</v>
       </c>
       <c r="C37" t="n">
-        <v>6.063062191009521</v>
+        <v>6.533514022827148</v>
       </c>
       <c r="D37" t="n">
-        <v>5.657605648040771</v>
+        <v>6.417345523834229</v>
       </c>
       <c r="E37" t="n">
-        <v>5.956867694854736</v>
+        <v>6.453724145889282</v>
       </c>
       <c r="F37" t="n">
-        <v>5.708968639373779</v>
+        <v>5.547070503234863</v>
       </c>
       <c r="G37" t="n">
-        <v>8.184057950973511</v>
+        <v>6.045292377471924</v>
       </c>
       <c r="H37" t="n">
-        <v>6.057060956954956</v>
+        <v>6.359473705291748</v>
       </c>
       <c r="I37" t="n">
-        <v>7.136325359344482</v>
+        <v>5.711637735366821</v>
       </c>
       <c r="J37" t="n">
-        <v>6.047598838806152</v>
+        <v>5.9388427734375</v>
       </c>
       <c r="K37" t="n">
-        <v>7.150798559188843</v>
+        <v>6.19110107421875</v>
       </c>
       <c r="L37" t="n">
-        <v>6.39097146987915</v>
+        <v>6.156393098831177</v>
       </c>
     </row>
     <row r="38">
@@ -3830,37 +3830,37 @@
         <v>42</v>
       </c>
       <c r="B38" t="n">
-        <v>6.253058433532715</v>
+        <v>8.458480358123779</v>
       </c>
       <c r="C38" t="n">
-        <v>6.810656070709229</v>
+        <v>6.490124225616455</v>
       </c>
       <c r="D38" t="n">
-        <v>7.742745637893677</v>
+        <v>6.32304310798645</v>
       </c>
       <c r="E38" t="n">
-        <v>6.509914875030518</v>
+        <v>7.728899240493774</v>
       </c>
       <c r="F38" t="n">
-        <v>8.424551486968994</v>
+        <v>6.259717226028442</v>
       </c>
       <c r="G38" t="n">
-        <v>8.003648281097412</v>
+        <v>8.93958854675293</v>
       </c>
       <c r="H38" t="n">
-        <v>8.260509014129639</v>
+        <v>6.196221351623535</v>
       </c>
       <c r="I38" t="n">
-        <v>6.503452301025391</v>
+        <v>7.431061983108521</v>
       </c>
       <c r="J38" t="n">
-        <v>9.447941541671753</v>
+        <v>6.720374822616577</v>
       </c>
       <c r="K38" t="n">
-        <v>8.019148349761963</v>
+        <v>8.799584150314331</v>
       </c>
       <c r="L38" t="n">
-        <v>7.597562599182129</v>
+        <v>7.334709501266479</v>
       </c>
     </row>
     <row r="39">
@@ -3868,37 +3868,37 @@
         <v>43</v>
       </c>
       <c r="B39" t="n">
-        <v>5.881205797195435</v>
+        <v>6.357819318771362</v>
       </c>
       <c r="C39" t="n">
-        <v>6.012362241744995</v>
+        <v>7.312889814376831</v>
       </c>
       <c r="D39" t="n">
-        <v>5.574522018432617</v>
+        <v>5.593255043029785</v>
       </c>
       <c r="E39" t="n">
-        <v>6.26376485824585</v>
+        <v>6.603223562240601</v>
       </c>
       <c r="F39" t="n">
-        <v>8.441058397293091</v>
+        <v>6.115929365158081</v>
       </c>
       <c r="G39" t="n">
-        <v>5.707664489746094</v>
+        <v>7.639558792114258</v>
       </c>
       <c r="H39" t="n">
-        <v>6.363460779190063</v>
+        <v>8.994090557098389</v>
       </c>
       <c r="I39" t="n">
-        <v>7.351386785507202</v>
+        <v>6.156338930130005</v>
       </c>
       <c r="J39" t="n">
-        <v>5.863273143768311</v>
+        <v>7.837069988250732</v>
       </c>
       <c r="K39" t="n">
-        <v>7.955803394317627</v>
+        <v>5.988742351531982</v>
       </c>
       <c r="L39" t="n">
-        <v>6.541450190544128</v>
+        <v>6.859891772270203</v>
       </c>
     </row>
     <row r="40">
@@ -3906,37 +3906,37 @@
         <v>44</v>
       </c>
       <c r="B40" t="n">
-        <v>6.803323745727539</v>
+        <v>6.600229024887085</v>
       </c>
       <c r="C40" t="n">
-        <v>6.537502527236938</v>
+        <v>7.059024333953857</v>
       </c>
       <c r="D40" t="n">
-        <v>9.447959899902344</v>
+        <v>6.450574398040771</v>
       </c>
       <c r="E40" t="n">
-        <v>6.962453842163086</v>
+        <v>6.70839524269104</v>
       </c>
       <c r="F40" t="n">
-        <v>8.7727370262146</v>
+        <v>8.84602427482605</v>
       </c>
       <c r="G40" t="n">
-        <v>9.09685206413269</v>
+        <v>6.803161382675171</v>
       </c>
       <c r="H40" t="n">
-        <v>8.347296714782715</v>
+        <v>9.644958257675171</v>
       </c>
       <c r="I40" t="n">
-        <v>6.42930793762207</v>
+        <v>6.684957981109619</v>
       </c>
       <c r="J40" t="n">
-        <v>6.66765832901001</v>
+        <v>6.39673113822937</v>
       </c>
       <c r="K40" t="n">
-        <v>7.946822881698608</v>
+        <v>5.950836420059204</v>
       </c>
       <c r="L40" t="n">
-        <v>7.70119149684906</v>
+        <v>7.114489245414734</v>
       </c>
     </row>
     <row r="41">
@@ -3944,37 +3944,37 @@
         <v>45</v>
       </c>
       <c r="B41" t="n">
-        <v>6.752566576004028</v>
+        <v>10.3182008266449</v>
       </c>
       <c r="C41" t="n">
-        <v>7.454024076461792</v>
+        <v>6.942801237106323</v>
       </c>
       <c r="D41" t="n">
-        <v>8.058035850524902</v>
+        <v>6.742320775985718</v>
       </c>
       <c r="E41" t="n">
-        <v>10.38208866119385</v>
+        <v>7.150188207626343</v>
       </c>
       <c r="F41" t="n">
-        <v>6.689507246017456</v>
+        <v>7.207747220993042</v>
       </c>
       <c r="G41" t="n">
-        <v>7.568286657333374</v>
+        <v>7.472059488296509</v>
       </c>
       <c r="H41" t="n">
-        <v>8.981643676757812</v>
+        <v>9.426467895507812</v>
       </c>
       <c r="I41" t="n">
-        <v>9.203072547912598</v>
+        <v>7.956816434860229</v>
       </c>
       <c r="J41" t="n">
-        <v>8.280263900756836</v>
+        <v>7.122979879379272</v>
       </c>
       <c r="K41" t="n">
-        <v>7.414600372314453</v>
+        <v>7.438072443008423</v>
       </c>
       <c r="L41" t="n">
-        <v>8.07840895652771</v>
+        <v>7.777765440940857</v>
       </c>
     </row>
     <row r="42">
@@ -3982,37 +3982,37 @@
         <v>46</v>
       </c>
       <c r="B42" t="n">
-        <v>5.700484991073608</v>
+        <v>5.431178092956543</v>
       </c>
       <c r="C42" t="n">
-        <v>6.477009296417236</v>
+        <v>5.601753711700439</v>
       </c>
       <c r="D42" t="n">
-        <v>5.524444103240967</v>
+        <v>5.460081577301025</v>
       </c>
       <c r="E42" t="n">
-        <v>5.752353668212891</v>
+        <v>6.613139390945435</v>
       </c>
       <c r="F42" t="n">
-        <v>6.869522571563721</v>
+        <v>5.371321678161621</v>
       </c>
       <c r="G42" t="n">
-        <v>5.59377646446228</v>
+        <v>8.816576242446899</v>
       </c>
       <c r="H42" t="n">
-        <v>6.217171192169189</v>
+        <v>5.734894514083862</v>
       </c>
       <c r="I42" t="n">
-        <v>5.960333347320557</v>
+        <v>7.651034116744995</v>
       </c>
       <c r="J42" t="n">
-        <v>5.125958919525146</v>
+        <v>5.245635032653809</v>
       </c>
       <c r="K42" t="n">
-        <v>5.180319786071777</v>
+        <v>5.45211935043335</v>
       </c>
       <c r="L42" t="n">
-        <v>5.840137434005737</v>
+        <v>6.137773370742797</v>
       </c>
     </row>
     <row r="43">
@@ -4020,37 +4020,37 @@
         <v>47</v>
       </c>
       <c r="B43" t="n">
-        <v>6.553343772888184</v>
+        <v>6.094972848892212</v>
       </c>
       <c r="C43" t="n">
-        <v>7.853004693984985</v>
+        <v>8.094897985458374</v>
       </c>
       <c r="D43" t="n">
-        <v>7.421092510223389</v>
+        <v>8.715317487716675</v>
       </c>
       <c r="E43" t="n">
-        <v>9.320781707763672</v>
+        <v>6.341387987136841</v>
       </c>
       <c r="F43" t="n">
-        <v>6.185266733169556</v>
+        <v>7.100407123565674</v>
       </c>
       <c r="G43" t="n">
-        <v>6.199227809906006</v>
+        <v>8.005606174468994</v>
       </c>
       <c r="H43" t="n">
-        <v>7.778692960739136</v>
+        <v>7.914450883865356</v>
       </c>
       <c r="I43" t="n">
-        <v>6.801665067672729</v>
+        <v>5.938362598419189</v>
       </c>
       <c r="J43" t="n">
-        <v>6.375746726989746</v>
+        <v>8.197098255157471</v>
       </c>
       <c r="K43" t="n">
-        <v>8.076486825942993</v>
+        <v>7.326825857162476</v>
       </c>
       <c r="L43" t="n">
-        <v>7.25653088092804</v>
+        <v>7.372932720184326</v>
       </c>
     </row>
     <row r="44">
@@ -4058,37 +4058,37 @@
         <v>48</v>
       </c>
       <c r="B44" t="n">
-        <v>6.738352298736572</v>
+        <v>8.705379247665405</v>
       </c>
       <c r="C44" t="n">
-        <v>8.504856824874878</v>
+        <v>6.698435544967651</v>
       </c>
       <c r="D44" t="n">
-        <v>6.460530042648315</v>
+        <v>6.570775270462036</v>
       </c>
       <c r="E44" t="n">
-        <v>8.434555292129517</v>
+        <v>8.884888887405396</v>
       </c>
       <c r="F44" t="n">
-        <v>7.620591402053833</v>
+        <v>9.839983224868774</v>
       </c>
       <c r="G44" t="n">
-        <v>7.391206026077271</v>
+        <v>6.564315319061279</v>
       </c>
       <c r="H44" t="n">
-        <v>7.275477886199951</v>
+        <v>6.316407442092896</v>
       </c>
       <c r="I44" t="n">
-        <v>7.853492498397827</v>
+        <v>6.804679870605469</v>
       </c>
       <c r="J44" t="n">
-        <v>7.622594118118286</v>
+        <v>6.489461183547974</v>
       </c>
       <c r="K44" t="n">
-        <v>7.89439868927002</v>
+        <v>6.368861436843872</v>
       </c>
       <c r="L44" t="n">
-        <v>7.579605507850647</v>
+        <v>7.324318742752075</v>
       </c>
     </row>
     <row r="45">
@@ -4096,37 +4096,37 @@
         <v>49</v>
       </c>
       <c r="B45" t="n">
-        <v>5.91445255279541</v>
+        <v>8.801571369171143</v>
       </c>
       <c r="C45" t="n">
-        <v>9.024027347564697</v>
+        <v>10.06833124160767</v>
       </c>
       <c r="D45" t="n">
-        <v>8.26795220375061</v>
+        <v>9.8449387550354</v>
       </c>
       <c r="E45" t="n">
-        <v>6.744860887527466</v>
+        <v>7.564732313156128</v>
       </c>
       <c r="F45" t="n">
-        <v>9.283343076705933</v>
+        <v>8.881859064102173</v>
       </c>
       <c r="G45" t="n">
-        <v>7.055550575256348</v>
+        <v>8.823526620864868</v>
       </c>
       <c r="H45" t="n">
-        <v>6.581714630126953</v>
+        <v>6.689972877502441</v>
       </c>
       <c r="I45" t="n">
-        <v>6.500989198684692</v>
+        <v>9.82796049118042</v>
       </c>
       <c r="J45" t="n">
-        <v>7.959205389022827</v>
+        <v>9.347202301025391</v>
       </c>
       <c r="K45" t="n">
-        <v>9.235003232955933</v>
+        <v>8.619071483612061</v>
       </c>
       <c r="L45" t="n">
-        <v>7.656709909439087</v>
+        <v>8.846916651725769</v>
       </c>
     </row>
     <row r="46">
@@ -4134,37 +4134,37 @@
         <v>5</v>
       </c>
       <c r="B46" t="n">
-        <v>7.407141447067261</v>
+        <v>6.758301973342896</v>
       </c>
       <c r="C46" t="n">
-        <v>8.015588283538818</v>
+        <v>6.773819923400879</v>
       </c>
       <c r="D46" t="n">
-        <v>6.538856029510498</v>
+        <v>8.207106828689575</v>
       </c>
       <c r="E46" t="n">
-        <v>8.373213291168213</v>
+        <v>6.927854061126709</v>
       </c>
       <c r="F46" t="n">
-        <v>7.85752272605896</v>
+        <v>7.08395528793335</v>
       </c>
       <c r="G46" t="n">
-        <v>7.631540775299072</v>
+        <v>8.451014041900635</v>
       </c>
       <c r="H46" t="n">
-        <v>9.109295606613159</v>
+        <v>9.092829704284668</v>
       </c>
       <c r="I46" t="n">
-        <v>7.773679971694946</v>
+        <v>8.50693941116333</v>
       </c>
       <c r="J46" t="n">
-        <v>7.1084144115448</v>
+        <v>6.652553081512451</v>
       </c>
       <c r="K46" t="n">
-        <v>6.269555330276489</v>
+        <v>8.021585464477539</v>
       </c>
       <c r="L46" t="n">
-        <v>7.608480787277221</v>
+        <v>7.647595977783203</v>
       </c>
     </row>
     <row r="47">
@@ -4172,37 +4172,37 @@
         <v>50</v>
       </c>
       <c r="B47" t="n">
-        <v>7.18869161605835</v>
+        <v>7.123372316360474</v>
       </c>
       <c r="C47" t="n">
-        <v>9.490857839584351</v>
+        <v>9.429005146026611</v>
       </c>
       <c r="D47" t="n">
-        <v>8.831030130386353</v>
+        <v>8.125810861587524</v>
       </c>
       <c r="E47" t="n">
-        <v>8.469408512115479</v>
+        <v>8.743199348449707</v>
       </c>
       <c r="F47" t="n">
-        <v>8.731297731399536</v>
+        <v>8.476930618286133</v>
       </c>
       <c r="G47" t="n">
-        <v>7.825492858886719</v>
+        <v>9.318746089935303</v>
       </c>
       <c r="H47" t="n">
-        <v>8.107412815093994</v>
+        <v>8.704296588897705</v>
       </c>
       <c r="I47" t="n">
-        <v>9.535691499710083</v>
+        <v>6.469510555267334</v>
       </c>
       <c r="J47" t="n">
-        <v>8.256068468093872</v>
+        <v>7.941256761550903</v>
       </c>
       <c r="K47" t="n">
-        <v>8.395624876022339</v>
+        <v>8.603096008300781</v>
       </c>
       <c r="L47" t="n">
-        <v>8.483157634735107</v>
+        <v>8.293522429466247</v>
       </c>
     </row>
     <row r="48">
@@ -4210,37 +4210,37 @@
         <v>6</v>
       </c>
       <c r="B48" t="n">
-        <v>6.44327449798584</v>
+        <v>6.277515172958374</v>
       </c>
       <c r="C48" t="n">
-        <v>5.882195711135864</v>
+        <v>6.487584590911865</v>
       </c>
       <c r="D48" t="n">
-        <v>7.519003391265869</v>
+        <v>8.622043132781982</v>
       </c>
       <c r="E48" t="n">
-        <v>6.638108253479004</v>
+        <v>8.550707340240479</v>
       </c>
       <c r="F48" t="n">
-        <v>8.032607555389404</v>
+        <v>10.39559054374695</v>
       </c>
       <c r="G48" t="n">
-        <v>6.746227502822876</v>
+        <v>7.044145107269287</v>
       </c>
       <c r="H48" t="n">
-        <v>6.72001576423645</v>
+        <v>7.31689190864563</v>
       </c>
       <c r="I48" t="n">
-        <v>6.404326200485229</v>
+        <v>6.675564289093018</v>
       </c>
       <c r="J48" t="n">
-        <v>8.88189959526062</v>
+        <v>6.969782829284668</v>
       </c>
       <c r="K48" t="n">
-        <v>6.232783079147339</v>
+        <v>6.084020853042603</v>
       </c>
       <c r="L48" t="n">
-        <v>6.95004415512085</v>
+        <v>7.442384576797485</v>
       </c>
     </row>
     <row r="49">
@@ -4248,37 +4248,37 @@
         <v>7</v>
       </c>
       <c r="B49" t="n">
-        <v>7.1309974193573</v>
+        <v>8.0998854637146</v>
       </c>
       <c r="C49" t="n">
-        <v>7.21624231338501</v>
+        <v>7.367262363433838</v>
       </c>
       <c r="D49" t="n">
-        <v>7.379316329956055</v>
+        <v>7.581184387207031</v>
       </c>
       <c r="E49" t="n">
-        <v>8.903340578079224</v>
+        <v>6.880970478057861</v>
       </c>
       <c r="F49" t="n">
-        <v>8.354758501052856</v>
+        <v>6.925827980041504</v>
       </c>
       <c r="G49" t="n">
-        <v>7.44613790512085</v>
+        <v>6.973257064819336</v>
       </c>
       <c r="H49" t="n">
-        <v>6.837211608886719</v>
+        <v>7.744752645492554</v>
       </c>
       <c r="I49" t="n">
-        <v>7.533906221389771</v>
+        <v>7.411362171173096</v>
       </c>
       <c r="J49" t="n">
-        <v>7.00380802154541</v>
+        <v>6.830320835113525</v>
       </c>
       <c r="K49" t="n">
-        <v>7.560885906219482</v>
+        <v>7.294527769088745</v>
       </c>
       <c r="L49" t="n">
-        <v>7.536660480499267</v>
+        <v>7.310935115814209</v>
       </c>
     </row>
     <row r="50">
@@ -4286,37 +4286,37 @@
         <v>8</v>
       </c>
       <c r="B50" t="n">
-        <v>8.917562007904053</v>
+        <v>8.236609220504761</v>
       </c>
       <c r="C50" t="n">
-        <v>9.275879144668579</v>
+        <v>6.797370910644531</v>
       </c>
       <c r="D50" t="n">
-        <v>7.979247093200684</v>
+        <v>9.890772342681885</v>
       </c>
       <c r="E50" t="n">
-        <v>6.911532640457153</v>
+        <v>8.123376369476318</v>
       </c>
       <c r="F50" t="n">
-        <v>12.28654098510742</v>
+        <v>10.72761058807373</v>
       </c>
       <c r="G50" t="n">
-        <v>7.052055597305298</v>
+        <v>9.223010778427124</v>
       </c>
       <c r="H50" t="n">
-        <v>9.280862808227539</v>
+        <v>9.326255083084106</v>
       </c>
       <c r="I50" t="n">
-        <v>9.628468036651611</v>
+        <v>9.353197574615479</v>
       </c>
       <c r="J50" t="n">
-        <v>8.593111753463745</v>
+        <v>7.078094482421875</v>
       </c>
       <c r="K50" t="n">
-        <v>7.645540475845337</v>
+        <v>8.783655881881714</v>
       </c>
       <c r="L50" t="n">
-        <v>8.757080054283142</v>
+        <v>8.753995323181153</v>
       </c>
     </row>
     <row r="51">
@@ -4324,37 +4324,37 @@
         <v>9</v>
       </c>
       <c r="B51" t="n">
-        <v>8.543715476989746</v>
+        <v>7.876999139785767</v>
       </c>
       <c r="C51" t="n">
-        <v>7.526324033737183</v>
+        <v>6.978157520294189</v>
       </c>
       <c r="D51" t="n">
-        <v>6.282502412796021</v>
+        <v>9.080915451049805</v>
       </c>
       <c r="E51" t="n">
-        <v>7.340807676315308</v>
+        <v>8.032544612884521</v>
       </c>
       <c r="F51" t="n">
-        <v>8.579184055328369</v>
+        <v>6.646592855453491</v>
       </c>
       <c r="G51" t="n">
-        <v>6.845572471618652</v>
+        <v>8.740259408950806</v>
       </c>
       <c r="H51" t="n">
-        <v>7.389215469360352</v>
+        <v>6.966733932495117</v>
       </c>
       <c r="I51" t="n">
-        <v>6.794183015823364</v>
+        <v>7.447517156600952</v>
       </c>
       <c r="J51" t="n">
-        <v>7.447547912597656</v>
+        <v>8.864389419555664</v>
       </c>
       <c r="K51" t="n">
-        <v>6.991187810897827</v>
+        <v>6.547838687896729</v>
       </c>
       <c r="L51" t="n">
-        <v>7.374024033546448</v>
+        <v>7.718194818496704</v>
       </c>
     </row>
     <row r="52">
@@ -4364,37 +4364,37 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>7.156882557868958</v>
+        <v>7.66428813457489</v>
       </c>
       <c r="C52" t="n">
-        <v>7.502470092773438</v>
+        <v>7.332078537940979</v>
       </c>
       <c r="D52" t="n">
-        <v>7.110603861808777</v>
+        <v>7.6427587890625</v>
       </c>
       <c r="E52" t="n">
-        <v>7.458940005302429</v>
+        <v>7.431609649658203</v>
       </c>
       <c r="F52" t="n">
-        <v>7.504511151313782</v>
+        <v>7.579629011154175</v>
       </c>
       <c r="G52" t="n">
-        <v>7.634035573005677</v>
+        <v>7.756865611076355</v>
       </c>
       <c r="H52" t="n">
-        <v>7.365813946723938</v>
+        <v>7.64916042804718</v>
       </c>
       <c r="I52" t="n">
-        <v>7.518259029388428</v>
+        <v>7.612014193534851</v>
       </c>
       <c r="J52" t="n">
-        <v>7.254063105583191</v>
+        <v>7.502006649971008</v>
       </c>
       <c r="K52" t="n">
-        <v>7.384994354248047</v>
+        <v>7.501549906730652</v>
       </c>
       <c r="L52" t="n">
-        <v>7.389057367801667</v>
+        <v>7.56719609117508</v>
       </c>
     </row>
   </sheetData>
